--- a/all reports/SST Report April,26(Dolphin Trader).xlsx
+++ b/all reports/SST Report April,26(Dolphin Trader).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite Traders\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262C830A-9BAB-4311-8CE5-482F4A43857D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DEA325D-9177-4ADA-82C0-A60B0F5F3171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
   <sheets>
     <sheet name="STT Report" sheetId="1" r:id="rId1"/>
@@ -1718,7 +1718,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1903,12 +1903,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1939,22 +1934,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1966,11 +1961,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2337,111 +2332,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="88" t="s">
+      <c r="A1" s="84" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="89" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="89" t="s">
+      <c r="C1" s="81" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="89" t="s">
+      <c r="E1" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="89" t="s">
+      <c r="F1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="88" t="s">
+      <c r="G1" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="89" t="s">
+      <c r="H1" s="81" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="88" t="s">
+      <c r="J1" s="71"/>
+      <c r="K1" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="93" t="s">
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="94"/>
-      <c r="S1" s="90" t="s">
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="92" t="s">
+      <c r="T1" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="92"/>
-      <c r="V1" s="92"/>
-      <c r="W1" s="92"/>
-      <c r="X1" s="92" t="s">
+      <c r="U1" s="89"/>
+      <c r="V1" s="89"/>
+      <c r="W1" s="89"/>
+      <c r="X1" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="92"/>
-      <c r="Z1" s="92"/>
-      <c r="AA1" s="92"/>
-      <c r="AB1" s="86" t="s">
+      <c r="Y1" s="89"/>
+      <c r="Z1" s="89"/>
+      <c r="AA1" s="89"/>
+      <c r="AB1" s="85" t="s">
         <v>378</v>
       </c>
-      <c r="AC1" s="86" t="s">
+      <c r="AC1" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="86" t="s">
+      <c r="AD1" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="86" t="s">
+      <c r="AE1" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="86" t="s">
+      <c r="AF1" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="86" t="s">
+      <c r="AG1" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="AH1" s="86" t="s">
+      <c r="AH1" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="AI1" s="86" t="s">
+      <c r="AI1" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="AJ1" s="86" t="s">
-        <v>20</v>
-      </c>
-      <c r="AK1" s="86" t="s">
+      <c r="AJ1" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="AK1" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="AL1" s="86" t="s">
+      <c r="AL1" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="AM1" s="84" t="s">
+      <c r="AM1" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="AN1" s="84" t="s">
+      <c r="AN1" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="AO1" s="86" t="s">
+      <c r="AO1" s="85" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:41" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="88"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="89"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="81"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -2472,7 +2467,7 @@
       <c r="R2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S2" s="91"/>
+      <c r="S2" s="88"/>
       <c r="T2" s="4" t="s">
         <v>35</v>
       </c>
@@ -2497,20 +2492,20 @@
       <c r="AA2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AB2" s="87"/>
-      <c r="AC2" s="87"/>
-      <c r="AD2" s="87"/>
-      <c r="AE2" s="87"/>
-      <c r="AF2" s="87"/>
-      <c r="AG2" s="87"/>
-      <c r="AH2" s="87"/>
-      <c r="AI2" s="87"/>
-      <c r="AJ2" s="87"/>
-      <c r="AK2" s="87"/>
-      <c r="AL2" s="87"/>
-      <c r="AM2" s="85"/>
-      <c r="AN2" s="85"/>
-      <c r="AO2" s="87"/>
+      <c r="AB2" s="86"/>
+      <c r="AC2" s="86"/>
+      <c r="AD2" s="86"/>
+      <c r="AE2" s="86"/>
+      <c r="AF2" s="86"/>
+      <c r="AG2" s="86"/>
+      <c r="AH2" s="86"/>
+      <c r="AI2" s="86"/>
+      <c r="AJ2" s="86"/>
+      <c r="AK2" s="86"/>
+      <c r="AL2" s="86"/>
+      <c r="AM2" s="91"/>
+      <c r="AN2" s="91"/>
+      <c r="AO2" s="86"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3" s="18">
@@ -2538,7 +2533,7 @@
         <v>339</v>
       </c>
       <c r="I3" s="7"/>
-      <c r="J3" s="75"/>
+      <c r="J3" s="72"/>
       <c r="K3" s="19">
         <v>20</v>
       </c>
@@ -2660,7 +2655,7 @@
         <v>339</v>
       </c>
       <c r="I4" s="7"/>
-      <c r="J4" s="75"/>
+      <c r="J4" s="72"/>
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
       <c r="M4" s="21"/>
@@ -2782,7 +2777,7 @@
         <v>340</v>
       </c>
       <c r="I5" s="7"/>
-      <c r="J5" s="75"/>
+      <c r="J5" s="72"/>
       <c r="K5" s="19">
         <v>20</v>
       </c>
@@ -2910,7 +2905,7 @@
         <v>340</v>
       </c>
       <c r="I6" s="7"/>
-      <c r="J6" s="75"/>
+      <c r="J6" s="72"/>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
       <c r="M6" s="21"/>
@@ -3028,7 +3023,7 @@
         <v>340</v>
       </c>
       <c r="I7" s="8"/>
-      <c r="J7" s="76"/>
+      <c r="J7" s="73"/>
       <c r="K7" s="21"/>
       <c r="L7" s="21"/>
       <c r="M7" s="21"/>
@@ -3159,7 +3154,7 @@
         <v>340</v>
       </c>
       <c r="I8" s="6"/>
-      <c r="J8" s="71"/>
+      <c r="J8" s="70"/>
       <c r="K8" s="19">
         <v>20</v>
       </c>
@@ -3285,7 +3280,7 @@
         <v>340</v>
       </c>
       <c r="I9" s="6"/>
-      <c r="J9" s="71"/>
+      <c r="J9" s="70"/>
       <c r="K9" s="19">
         <v>40</v>
       </c>
@@ -3411,7 +3406,7 @@
         <v>340</v>
       </c>
       <c r="I10" s="6"/>
-      <c r="J10" s="71"/>
+      <c r="J10" s="70"/>
       <c r="K10" s="19">
         <v>20</v>
       </c>
@@ -3536,7 +3531,7 @@
         <v>342</v>
       </c>
       <c r="I11" s="6"/>
-      <c r="J11" s="71"/>
+      <c r="J11" s="70"/>
       <c r="K11" s="21"/>
       <c r="L11" s="21"/>
       <c r="M11" s="21"/>
@@ -3651,7 +3646,7 @@
         <v>341</v>
       </c>
       <c r="I12" s="6"/>
-      <c r="J12" s="71"/>
+      <c r="J12" s="70"/>
       <c r="K12" s="19">
         <v>10</v>
       </c>
@@ -3768,7 +3763,7 @@
         <v>341</v>
       </c>
       <c r="I13" s="6"/>
-      <c r="J13" s="71"/>
+      <c r="J13" s="70"/>
       <c r="K13" s="19">
         <v>10</v>
       </c>
@@ -3887,7 +3882,7 @@
         <v>341</v>
       </c>
       <c r="I14" s="6"/>
-      <c r="J14" s="71"/>
+      <c r="J14" s="70"/>
       <c r="K14" s="19">
         <v>10</v>
       </c>
@@ -4006,7 +4001,7 @@
         <v>341</v>
       </c>
       <c r="I15" s="6"/>
-      <c r="J15" s="71"/>
+      <c r="J15" s="70"/>
       <c r="K15" s="21"/>
       <c r="L15" s="21"/>
       <c r="M15" s="21"/>
@@ -4125,7 +4120,7 @@
         <v>341</v>
       </c>
       <c r="I16" s="6"/>
-      <c r="J16" s="71"/>
+      <c r="J16" s="70"/>
       <c r="K16" s="19">
         <v>20</v>
       </c>
@@ -4246,7 +4241,7 @@
         <v>341</v>
       </c>
       <c r="I17" s="6"/>
-      <c r="J17" s="71"/>
+      <c r="J17" s="70"/>
       <c r="K17" s="21"/>
       <c r="L17" s="21"/>
       <c r="M17" s="21"/>
@@ -4361,7 +4356,7 @@
         <v>341</v>
       </c>
       <c r="I18" s="6"/>
-      <c r="J18" s="71"/>
+      <c r="J18" s="70"/>
       <c r="K18" s="21"/>
       <c r="L18" s="21"/>
       <c r="M18" s="21"/>
@@ -4478,7 +4473,7 @@
         <v>341</v>
       </c>
       <c r="I19" s="6"/>
-      <c r="J19" s="71"/>
+      <c r="J19" s="70"/>
       <c r="K19" s="19">
         <v>20</v>
       </c>
@@ -4603,7 +4598,7 @@
         <v>341</v>
       </c>
       <c r="I20" s="6"/>
-      <c r="J20" s="71"/>
+      <c r="J20" s="70"/>
       <c r="K20" s="21"/>
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
@@ -4722,7 +4717,7 @@
         <v>341</v>
       </c>
       <c r="I21" s="6"/>
-      <c r="J21" s="71"/>
+      <c r="J21" s="70"/>
       <c r="K21" s="19">
         <v>20</v>
       </c>
@@ -4847,7 +4842,7 @@
         <v>341</v>
       </c>
       <c r="I22" s="6"/>
-      <c r="J22" s="71"/>
+      <c r="J22" s="70"/>
       <c r="K22" s="19">
         <v>20</v>
       </c>
@@ -4972,7 +4967,7 @@
         <v>341</v>
       </c>
       <c r="I23" s="6"/>
-      <c r="J23" s="71"/>
+      <c r="J23" s="70"/>
       <c r="K23" s="19">
         <v>0</v>
       </c>
@@ -5093,7 +5088,7 @@
         <v>340</v>
       </c>
       <c r="I24" s="6"/>
-      <c r="J24" s="71"/>
+      <c r="J24" s="70"/>
       <c r="K24" s="21"/>
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
@@ -5212,7 +5207,7 @@
         <v>340</v>
       </c>
       <c r="I25" s="6"/>
-      <c r="J25" s="71"/>
+      <c r="J25" s="70"/>
       <c r="K25" s="19">
         <v>120</v>
       </c>
@@ -5333,7 +5328,7 @@
         <v>340</v>
       </c>
       <c r="I26" s="6"/>
-      <c r="J26" s="71"/>
+      <c r="J26" s="70"/>
       <c r="K26" s="19">
         <v>40</v>
       </c>
@@ -5458,7 +5453,7 @@
         <v>341</v>
       </c>
       <c r="I27" s="6"/>
-      <c r="J27" s="71"/>
+      <c r="J27" s="70"/>
       <c r="K27" s="21"/>
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
@@ -5575,7 +5570,7 @@
         <v>341</v>
       </c>
       <c r="I28" s="6"/>
-      <c r="J28" s="71"/>
+      <c r="J28" s="70"/>
       <c r="K28" s="21"/>
       <c r="L28" s="21"/>
       <c r="M28" s="21"/>
@@ -5692,7 +5687,7 @@
         <v>341</v>
       </c>
       <c r="I29" s="6"/>
-      <c r="J29" s="71"/>
+      <c r="J29" s="70"/>
       <c r="K29" s="21"/>
       <c r="L29" s="21"/>
       <c r="M29" s="21"/>
@@ -5811,7 +5806,7 @@
         <v>341</v>
       </c>
       <c r="I30" s="6"/>
-      <c r="J30" s="71"/>
+      <c r="J30" s="70"/>
       <c r="K30" s="21"/>
       <c r="L30" s="21"/>
       <c r="M30" s="21"/>
@@ -5926,7 +5921,7 @@
         <v>341</v>
       </c>
       <c r="I31" s="6"/>
-      <c r="J31" s="71"/>
+      <c r="J31" s="70"/>
       <c r="K31" s="21"/>
       <c r="L31" s="21"/>
       <c r="M31" s="21"/>
@@ -6043,7 +6038,7 @@
         <v>341</v>
       </c>
       <c r="I32" s="6"/>
-      <c r="J32" s="71"/>
+      <c r="J32" s="70"/>
       <c r="K32" s="21"/>
       <c r="L32" s="21"/>
       <c r="M32" s="21"/>
@@ -6160,7 +6155,7 @@
         <v>341</v>
       </c>
       <c r="I33" s="6"/>
-      <c r="J33" s="71"/>
+      <c r="J33" s="70"/>
       <c r="K33" s="21"/>
       <c r="L33" s="21"/>
       <c r="M33" s="21"/>
@@ -6279,7 +6274,7 @@
         <v>341</v>
       </c>
       <c r="I34" s="6"/>
-      <c r="J34" s="71"/>
+      <c r="J34" s="70"/>
       <c r="K34" s="21"/>
       <c r="L34" s="21"/>
       <c r="M34" s="21"/>
@@ -6396,7 +6391,7 @@
         <v>341</v>
       </c>
       <c r="I35" s="6"/>
-      <c r="J35" s="71"/>
+      <c r="J35" s="70"/>
       <c r="K35" s="19">
         <v>10</v>
       </c>
@@ -6521,7 +6516,7 @@
         <v>341</v>
       </c>
       <c r="I36" s="6"/>
-      <c r="J36" s="71"/>
+      <c r="J36" s="70"/>
       <c r="K36" s="19">
         <v>20</v>
       </c>
@@ -6640,7 +6635,7 @@
         <v>341</v>
       </c>
       <c r="I37" s="6"/>
-      <c r="J37" s="71"/>
+      <c r="J37" s="70"/>
       <c r="K37" s="19">
         <v>13</v>
       </c>
@@ -6757,7 +6752,7 @@
         <v>341</v>
       </c>
       <c r="I38" s="6"/>
-      <c r="J38" s="71"/>
+      <c r="J38" s="70"/>
       <c r="K38" s="21"/>
       <c r="L38" s="21"/>
       <c r="M38" s="21"/>
@@ -6876,7 +6871,7 @@
         <v>341</v>
       </c>
       <c r="I39" s="6"/>
-      <c r="J39" s="71"/>
+      <c r="J39" s="70"/>
       <c r="K39" s="21"/>
       <c r="L39" s="21"/>
       <c r="M39" s="21"/>
@@ -6995,7 +6990,7 @@
         <v>341</v>
       </c>
       <c r="I40" s="6"/>
-      <c r="J40" s="71"/>
+      <c r="J40" s="70"/>
       <c r="K40" s="21"/>
       <c r="L40" s="21"/>
       <c r="M40" s="21"/>
@@ -7112,7 +7107,7 @@
         <v>341</v>
       </c>
       <c r="I41" s="6"/>
-      <c r="J41" s="71"/>
+      <c r="J41" s="70"/>
       <c r="K41" s="21"/>
       <c r="L41" s="21"/>
       <c r="M41" s="21"/>
@@ -7231,7 +7226,7 @@
         <v>342</v>
       </c>
       <c r="I42" s="6"/>
-      <c r="J42" s="71"/>
+      <c r="J42" s="70"/>
       <c r="K42" s="21"/>
       <c r="L42" s="21"/>
       <c r="M42" s="19">
@@ -7348,7 +7343,7 @@
         <v>339</v>
       </c>
       <c r="I43" s="6"/>
-      <c r="J43" s="71"/>
+      <c r="J43" s="70"/>
       <c r="K43" s="19">
         <v>20</v>
       </c>
@@ -7473,7 +7468,7 @@
         <v>339</v>
       </c>
       <c r="I44" s="6"/>
-      <c r="J44" s="71"/>
+      <c r="J44" s="70"/>
       <c r="K44" s="21"/>
       <c r="L44" s="21"/>
       <c r="M44" s="21"/>
@@ -7590,7 +7585,7 @@
         <v>339</v>
       </c>
       <c r="I45" s="6"/>
-      <c r="J45" s="71"/>
+      <c r="J45" s="70"/>
       <c r="K45" s="19">
         <v>10</v>
       </c>
@@ -7707,7 +7702,7 @@
         <v>339</v>
       </c>
       <c r="I46" s="6"/>
-      <c r="J46" s="71"/>
+      <c r="J46" s="70"/>
       <c r="K46" s="19">
         <v>20</v>
       </c>
@@ -7832,7 +7827,7 @@
         <v>340</v>
       </c>
       <c r="I47" s="6"/>
-      <c r="J47" s="71"/>
+      <c r="J47" s="70"/>
       <c r="K47" s="21"/>
       <c r="L47" s="21"/>
       <c r="M47" s="21"/>
@@ -7947,7 +7942,7 @@
         <v>340</v>
       </c>
       <c r="I48" s="6"/>
-      <c r="J48" s="71"/>
+      <c r="J48" s="70"/>
       <c r="K48" s="21"/>
       <c r="L48" s="21"/>
       <c r="M48" s="21"/>
@@ -8064,7 +8059,7 @@
         <v>340</v>
       </c>
       <c r="I49" s="6"/>
-      <c r="J49" s="71"/>
+      <c r="J49" s="70"/>
       <c r="K49" s="21"/>
       <c r="L49" s="21"/>
       <c r="M49" s="21"/>
@@ -8181,7 +8176,7 @@
         <v>340</v>
       </c>
       <c r="I50" s="6"/>
-      <c r="J50" s="71"/>
+      <c r="J50" s="70"/>
       <c r="K50" s="19">
         <v>20</v>
       </c>
@@ -8300,7 +8295,7 @@
         <v>340</v>
       </c>
       <c r="I51" s="6"/>
-      <c r="J51" s="71"/>
+      <c r="J51" s="70"/>
       <c r="K51" s="21"/>
       <c r="L51" s="21"/>
       <c r="M51" s="21"/>
@@ -8415,7 +8410,7 @@
         <v>342</v>
       </c>
       <c r="I52" s="6"/>
-      <c r="J52" s="71"/>
+      <c r="J52" s="70"/>
       <c r="K52" s="21"/>
       <c r="L52" s="19">
         <v>40</v>
@@ -8536,7 +8531,7 @@
         <v>342</v>
       </c>
       <c r="I53" s="6"/>
-      <c r="J53" s="71"/>
+      <c r="J53" s="70"/>
       <c r="K53" s="21"/>
       <c r="L53" s="19">
         <v>1</v>
@@ -8659,7 +8654,7 @@
         <v>342</v>
       </c>
       <c r="I54" s="6"/>
-      <c r="J54" s="71"/>
+      <c r="J54" s="70"/>
       <c r="K54" s="21"/>
       <c r="L54" s="21"/>
       <c r="M54" s="21"/>
@@ -8774,7 +8769,7 @@
         <v>341</v>
       </c>
       <c r="I55" s="6"/>
-      <c r="J55" s="71"/>
+      <c r="J55" s="70"/>
       <c r="K55" s="19">
         <v>10</v>
       </c>
@@ -8899,7 +8894,7 @@
         <v>341</v>
       </c>
       <c r="I56" s="6"/>
-      <c r="J56" s="71"/>
+      <c r="J56" s="70"/>
       <c r="K56" s="21"/>
       <c r="L56" s="21"/>
       <c r="M56" s="21"/>
@@ -9018,7 +9013,7 @@
         <v>341</v>
       </c>
       <c r="I57" s="6"/>
-      <c r="J57" s="71"/>
+      <c r="J57" s="70"/>
       <c r="K57" s="19">
         <v>120</v>
       </c>
@@ -9143,7 +9138,7 @@
         <v>341</v>
       </c>
       <c r="I58" s="6"/>
-      <c r="J58" s="71"/>
+      <c r="J58" s="70"/>
       <c r="K58" s="21"/>
       <c r="L58" s="21"/>
       <c r="M58" s="21"/>
@@ -9260,7 +9255,7 @@
         <v>341</v>
       </c>
       <c r="I59" s="6"/>
-      <c r="J59" s="71"/>
+      <c r="J59" s="70"/>
       <c r="K59" s="21"/>
       <c r="L59" s="21"/>
       <c r="M59" s="21"/>
@@ -9377,7 +9372,7 @@
         <v>341</v>
       </c>
       <c r="I60" s="6"/>
-      <c r="J60" s="71"/>
+      <c r="J60" s="70"/>
       <c r="K60" s="21"/>
       <c r="L60" s="21"/>
       <c r="M60" s="21"/>
@@ -9494,7 +9489,7 @@
         <v>341</v>
       </c>
       <c r="I61" s="6"/>
-      <c r="J61" s="71"/>
+      <c r="J61" s="70"/>
       <c r="K61" s="21"/>
       <c r="L61" s="21"/>
       <c r="M61" s="21"/>
@@ -9613,7 +9608,7 @@
         <v>341</v>
       </c>
       <c r="I62" s="6"/>
-      <c r="J62" s="71"/>
+      <c r="J62" s="70"/>
       <c r="K62" s="21"/>
       <c r="L62" s="21"/>
       <c r="M62" s="21"/>
@@ -9732,7 +9727,7 @@
         <v>341</v>
       </c>
       <c r="I63" s="6"/>
-      <c r="J63" s="71"/>
+      <c r="J63" s="70"/>
       <c r="K63" s="19">
         <v>20</v>
       </c>
@@ -9857,7 +9852,7 @@
         <v>341</v>
       </c>
       <c r="I64" s="6"/>
-      <c r="J64" s="71"/>
+      <c r="J64" s="70"/>
       <c r="K64" s="21"/>
       <c r="L64" s="19">
         <v>20</v>
@@ -9974,7 +9969,7 @@
         <v>341</v>
       </c>
       <c r="I65" s="6"/>
-      <c r="J65" s="71"/>
+      <c r="J65" s="70"/>
       <c r="K65" s="21"/>
       <c r="L65" s="21"/>
       <c r="M65" s="21"/>
@@ -10091,7 +10086,7 @@
         <v>341</v>
       </c>
       <c r="I66" s="6"/>
-      <c r="J66" s="71"/>
+      <c r="J66" s="70"/>
       <c r="K66" s="19">
         <v>20</v>
       </c>
@@ -10216,7 +10211,7 @@
         <v>341</v>
       </c>
       <c r="I67" s="6"/>
-      <c r="J67" s="71"/>
+      <c r="J67" s="70"/>
       <c r="K67" s="21"/>
       <c r="L67" s="21"/>
       <c r="M67" s="21"/>
@@ -10335,7 +10330,7 @@
         <v>341</v>
       </c>
       <c r="I68" s="6"/>
-      <c r="J68" s="71"/>
+      <c r="J68" s="70"/>
       <c r="K68" s="19">
         <v>20</v>
       </c>
@@ -10454,7 +10449,7 @@
         <v>339</v>
       </c>
       <c r="I69" s="6"/>
-      <c r="J69" s="71"/>
+      <c r="J69" s="70"/>
       <c r="K69" s="19">
         <v>20</v>
       </c>
@@ -10569,7 +10564,7 @@
         <v>339</v>
       </c>
       <c r="I70" s="6"/>
-      <c r="J70" s="71"/>
+      <c r="J70" s="70"/>
       <c r="K70" s="21"/>
       <c r="L70" s="21"/>
       <c r="M70" s="21"/>
@@ -10686,7 +10681,7 @@
         <v>339</v>
       </c>
       <c r="I71" s="6"/>
-      <c r="J71" s="71"/>
+      <c r="J71" s="70"/>
       <c r="K71" s="19">
         <v>40</v>
       </c>
@@ -10811,7 +10806,7 @@
         <v>339</v>
       </c>
       <c r="I72" s="6"/>
-      <c r="J72" s="71"/>
+      <c r="J72" s="70"/>
       <c r="K72" s="21"/>
       <c r="L72" s="21"/>
       <c r="M72" s="21"/>
@@ -10930,7 +10925,7 @@
         <v>339</v>
       </c>
       <c r="I73" s="6"/>
-      <c r="J73" s="71"/>
+      <c r="J73" s="70"/>
       <c r="K73" s="19">
         <v>0</v>
       </c>
@@ -11055,7 +11050,7 @@
         <v>339</v>
       </c>
       <c r="I74" s="6"/>
-      <c r="J74" s="71"/>
+      <c r="J74" s="70"/>
       <c r="K74" s="19">
         <v>20</v>
       </c>
@@ -11174,7 +11169,7 @@
         <v>339</v>
       </c>
       <c r="I75" s="6"/>
-      <c r="J75" s="71"/>
+      <c r="J75" s="70"/>
       <c r="K75" s="21"/>
       <c r="L75" s="21"/>
       <c r="M75" s="21"/>
@@ -11293,7 +11288,7 @@
         <v>339</v>
       </c>
       <c r="I76" s="6"/>
-      <c r="J76" s="71"/>
+      <c r="J76" s="70"/>
       <c r="K76" s="19">
         <v>20</v>
       </c>
@@ -11418,7 +11413,7 @@
         <v>339</v>
       </c>
       <c r="I77" s="6"/>
-      <c r="J77" s="71"/>
+      <c r="J77" s="70"/>
       <c r="K77" s="21"/>
       <c r="L77" s="21"/>
       <c r="M77" s="21"/>
@@ -11535,7 +11530,7 @@
         <v>339</v>
       </c>
       <c r="I78" s="6"/>
-      <c r="J78" s="71"/>
+      <c r="J78" s="70"/>
       <c r="K78" s="21"/>
       <c r="L78" s="21"/>
       <c r="M78" s="21"/>
@@ -11654,7 +11649,7 @@
         <v>339</v>
       </c>
       <c r="I79" s="6"/>
-      <c r="J79" s="71"/>
+      <c r="J79" s="70"/>
       <c r="K79" s="21"/>
       <c r="L79" s="21"/>
       <c r="M79" s="21"/>
@@ -11771,7 +11766,7 @@
         <v>339</v>
       </c>
       <c r="I80" s="6"/>
-      <c r="J80" s="71"/>
+      <c r="J80" s="70"/>
       <c r="K80" s="21"/>
       <c r="L80" s="21"/>
       <c r="M80" s="21"/>
@@ -11886,7 +11881,7 @@
         <v>342</v>
       </c>
       <c r="I81" s="6"/>
-      <c r="J81" s="71"/>
+      <c r="J81" s="70"/>
       <c r="K81" s="19">
         <v>40</v>
       </c>
@@ -12011,7 +12006,7 @@
         <v>342</v>
       </c>
       <c r="I82" s="6"/>
-      <c r="J82" s="71"/>
+      <c r="J82" s="70"/>
       <c r="K82" s="19">
         <v>40</v>
       </c>
@@ -12136,7 +12131,7 @@
         <v>341</v>
       </c>
       <c r="I83" s="6"/>
-      <c r="J83" s="71"/>
+      <c r="J83" s="70"/>
       <c r="K83" s="19">
         <v>0</v>
       </c>
@@ -12255,7 +12250,7 @@
         <v>341</v>
       </c>
       <c r="I84" s="6"/>
-      <c r="J84" s="71"/>
+      <c r="J84" s="70"/>
       <c r="K84" s="21"/>
       <c r="L84" s="21"/>
       <c r="M84" s="21"/>
@@ -12374,7 +12369,7 @@
         <v>341</v>
       </c>
       <c r="I85" s="6"/>
-      <c r="J85" s="71"/>
+      <c r="J85" s="70"/>
       <c r="K85" s="19">
         <v>20</v>
       </c>
@@ -12493,7 +12488,7 @@
         <v>341</v>
       </c>
       <c r="I86" s="6"/>
-      <c r="J86" s="71"/>
+      <c r="J86" s="70"/>
       <c r="K86" s="19">
         <v>20</v>
       </c>
@@ -12610,7 +12605,7 @@
         <v>341</v>
       </c>
       <c r="I87" s="6"/>
-      <c r="J87" s="71"/>
+      <c r="J87" s="70"/>
       <c r="K87" s="21"/>
       <c r="L87" s="21"/>
       <c r="M87" s="19">
@@ -12727,7 +12722,7 @@
         <v>341</v>
       </c>
       <c r="I88" s="6"/>
-      <c r="J88" s="71"/>
+      <c r="J88" s="70"/>
       <c r="K88" s="19">
         <v>20</v>
       </c>
@@ -12846,7 +12841,7 @@
         <v>341</v>
       </c>
       <c r="I89" s="6"/>
-      <c r="J89" s="71"/>
+      <c r="J89" s="70"/>
       <c r="K89" s="21"/>
       <c r="L89" s="21"/>
       <c r="M89" s="21"/>
@@ -12965,7 +12960,7 @@
         <v>341</v>
       </c>
       <c r="I90" s="6"/>
-      <c r="J90" s="71"/>
+      <c r="J90" s="70"/>
       <c r="K90" s="19">
         <v>20</v>
       </c>
@@ -13084,7 +13079,7 @@
         <v>341</v>
       </c>
       <c r="I91" s="6"/>
-      <c r="J91" s="71"/>
+      <c r="J91" s="70"/>
       <c r="K91" s="21"/>
       <c r="L91" s="21"/>
       <c r="M91" s="21"/>
@@ -13203,7 +13198,7 @@
         <v>341</v>
       </c>
       <c r="I92" s="6"/>
-      <c r="J92" s="71"/>
+      <c r="J92" s="70"/>
       <c r="K92" s="19">
         <v>10</v>
       </c>
@@ -13320,7 +13315,7 @@
         <v>341</v>
       </c>
       <c r="I93" s="6"/>
-      <c r="J93" s="71"/>
+      <c r="J93" s="70"/>
       <c r="K93" s="19">
         <v>20</v>
       </c>
@@ -13439,7 +13434,7 @@
         <v>341</v>
       </c>
       <c r="I94" s="6"/>
-      <c r="J94" s="71"/>
+      <c r="J94" s="70"/>
       <c r="K94" s="21"/>
       <c r="L94" s="21"/>
       <c r="M94" s="21"/>
@@ -13558,7 +13553,7 @@
         <v>341</v>
       </c>
       <c r="I95" s="6"/>
-      <c r="J95" s="71"/>
+      <c r="J95" s="70"/>
       <c r="K95" s="21"/>
       <c r="L95" s="21"/>
       <c r="M95" s="21"/>
@@ -13677,7 +13672,7 @@
         <v>341</v>
       </c>
       <c r="I96" s="6"/>
-      <c r="J96" s="71"/>
+      <c r="J96" s="70"/>
       <c r="K96" s="19">
         <v>10</v>
       </c>
@@ -13802,7 +13797,7 @@
         <v>341</v>
       </c>
       <c r="I97" s="6"/>
-      <c r="J97" s="71"/>
+      <c r="J97" s="70"/>
       <c r="K97" s="21"/>
       <c r="L97" s="21"/>
       <c r="M97" s="21"/>
@@ -13921,7 +13916,7 @@
         <v>341</v>
       </c>
       <c r="I98" s="6"/>
-      <c r="J98" s="71"/>
+      <c r="J98" s="70"/>
       <c r="K98" s="19">
         <v>40</v>
       </c>
@@ -14046,7 +14041,7 @@
         <v>341</v>
       </c>
       <c r="I99" s="6"/>
-      <c r="J99" s="71"/>
+      <c r="J99" s="70"/>
       <c r="K99" s="19">
         <v>40</v>
       </c>
@@ -14163,7 +14158,7 @@
         <v>341</v>
       </c>
       <c r="I100" s="6"/>
-      <c r="J100" s="71"/>
+      <c r="J100" s="70"/>
       <c r="K100" s="21"/>
       <c r="L100" s="19">
         <v>10</v>
@@ -14278,7 +14273,7 @@
         <v>341</v>
       </c>
       <c r="I101" s="6"/>
-      <c r="J101" s="71"/>
+      <c r="J101" s="70"/>
       <c r="K101" s="21"/>
       <c r="L101" s="21"/>
       <c r="M101" s="21"/>
@@ -14397,7 +14392,7 @@
         <v>341</v>
       </c>
       <c r="I102" s="6"/>
-      <c r="J102" s="71"/>
+      <c r="J102" s="70"/>
       <c r="K102" s="19">
         <v>10</v>
       </c>
@@ -14522,7 +14517,7 @@
         <v>341</v>
       </c>
       <c r="I103" s="6"/>
-      <c r="J103" s="71"/>
+      <c r="J103" s="70"/>
       <c r="K103" s="19">
         <v>0</v>
       </c>
@@ -14647,7 +14642,7 @@
         <v>340</v>
       </c>
       <c r="I104" s="6"/>
-      <c r="J104" s="71"/>
+      <c r="J104" s="70"/>
       <c r="K104" s="19">
         <v>20</v>
       </c>
@@ -14772,7 +14767,7 @@
         <v>340</v>
       </c>
       <c r="I105" s="6"/>
-      <c r="J105" s="71"/>
+      <c r="J105" s="70"/>
       <c r="K105" s="21"/>
       <c r="L105" s="21"/>
       <c r="M105" s="21"/>
@@ -14889,7 +14884,7 @@
         <v>340</v>
       </c>
       <c r="I106" s="6"/>
-      <c r="J106" s="71"/>
+      <c r="J106" s="70"/>
       <c r="K106" s="19">
         <v>20</v>
       </c>
@@ -15014,7 +15009,7 @@
         <v>340</v>
       </c>
       <c r="I107" s="6"/>
-      <c r="J107" s="71"/>
+      <c r="J107" s="70"/>
       <c r="K107" s="21"/>
       <c r="L107" s="21"/>
       <c r="M107" s="21"/>
@@ -15131,7 +15126,7 @@
         <v>340</v>
       </c>
       <c r="I108" s="6"/>
-      <c r="J108" s="71"/>
+      <c r="J108" s="70"/>
       <c r="K108" s="21"/>
       <c r="L108" s="21"/>
       <c r="M108" s="21"/>
@@ -15250,7 +15245,7 @@
         <v>340</v>
       </c>
       <c r="I109" s="6"/>
-      <c r="J109" s="71"/>
+      <c r="J109" s="70"/>
       <c r="K109" s="19">
         <v>20</v>
       </c>
@@ -15367,7 +15362,7 @@
         <v>340</v>
       </c>
       <c r="I110" s="6"/>
-      <c r="J110" s="71"/>
+      <c r="J110" s="70"/>
       <c r="K110" s="19">
         <v>20</v>
       </c>
@@ -15486,7 +15481,7 @@
         <v>341</v>
       </c>
       <c r="I111" s="6"/>
-      <c r="J111" s="71"/>
+      <c r="J111" s="70"/>
       <c r="K111" s="21"/>
       <c r="L111" s="21"/>
       <c r="M111" s="21"/>
@@ -15605,7 +15600,7 @@
         <v>341</v>
       </c>
       <c r="I112" s="6"/>
-      <c r="J112" s="71"/>
+      <c r="J112" s="70"/>
       <c r="K112" s="21"/>
       <c r="L112" s="21"/>
       <c r="M112" s="21"/>
@@ -15724,7 +15719,7 @@
         <v>341</v>
       </c>
       <c r="I113" s="6"/>
-      <c r="J113" s="71"/>
+      <c r="J113" s="70"/>
       <c r="K113" s="21"/>
       <c r="L113" s="21"/>
       <c r="M113" s="21"/>
@@ -15843,7 +15838,7 @@
         <v>341</v>
       </c>
       <c r="I114" s="6"/>
-      <c r="J114" s="71"/>
+      <c r="J114" s="70"/>
       <c r="K114" s="21"/>
       <c r="L114" s="21"/>
       <c r="M114" s="21"/>
@@ -15962,7 +15957,7 @@
         <v>341</v>
       </c>
       <c r="I115" s="6"/>
-      <c r="J115" s="71"/>
+      <c r="J115" s="70"/>
       <c r="K115" s="19">
         <v>0</v>
       </c>
@@ -16085,7 +16080,7 @@
         <v>341</v>
       </c>
       <c r="I116" s="6"/>
-      <c r="J116" s="71"/>
+      <c r="J116" s="70"/>
       <c r="K116" s="19">
         <v>20</v>
       </c>
@@ -16208,7 +16203,7 @@
         <v>341</v>
       </c>
       <c r="I117" s="6"/>
-      <c r="J117" s="71"/>
+      <c r="J117" s="70"/>
       <c r="K117" s="19">
         <v>40</v>
       </c>
@@ -16329,7 +16324,7 @@
         <v>341</v>
       </c>
       <c r="I118" s="6"/>
-      <c r="J118" s="71"/>
+      <c r="J118" s="70"/>
       <c r="K118" s="21"/>
       <c r="L118" s="21"/>
       <c r="M118" s="21"/>
@@ -16444,7 +16439,7 @@
         <v>341</v>
       </c>
       <c r="I119" s="6"/>
-      <c r="J119" s="71"/>
+      <c r="J119" s="70"/>
       <c r="K119" s="21"/>
       <c r="L119" s="21"/>
       <c r="M119" s="21"/>
@@ -16559,7 +16554,7 @@
         <v>341</v>
       </c>
       <c r="I120" s="6"/>
-      <c r="J120" s="71"/>
+      <c r="J120" s="70"/>
       <c r="K120" s="19">
         <v>20</v>
       </c>
@@ -16684,7 +16679,7 @@
         <v>341</v>
       </c>
       <c r="I121" s="6"/>
-      <c r="J121" s="71"/>
+      <c r="J121" s="70"/>
       <c r="K121" s="19">
         <v>40</v>
       </c>
@@ -16803,7 +16798,7 @@
         <v>341</v>
       </c>
       <c r="I122" s="6"/>
-      <c r="J122" s="71"/>
+      <c r="J122" s="70"/>
       <c r="K122" s="21"/>
       <c r="L122" s="21"/>
       <c r="M122" s="21"/>
@@ -16918,7 +16913,7 @@
         <v>341</v>
       </c>
       <c r="I123" s="6"/>
-      <c r="J123" s="71"/>
+      <c r="J123" s="70"/>
       <c r="K123" s="21"/>
       <c r="L123" s="21"/>
       <c r="M123" s="21"/>
@@ -17037,7 +17032,7 @@
         <v>342</v>
       </c>
       <c r="I124" s="6"/>
-      <c r="J124" s="71"/>
+      <c r="J124" s="70"/>
       <c r="K124" s="21"/>
       <c r="L124" s="21"/>
       <c r="M124" s="21"/>
@@ -17154,7 +17149,7 @@
         <v>340</v>
       </c>
       <c r="I125" s="6"/>
-      <c r="J125" s="71"/>
+      <c r="J125" s="70"/>
       <c r="K125" s="19">
         <v>20</v>
       </c>
@@ -17273,7 +17268,7 @@
         <v>340</v>
       </c>
       <c r="I126" s="6"/>
-      <c r="J126" s="71"/>
+      <c r="J126" s="70"/>
       <c r="K126" s="21"/>
       <c r="L126" s="21"/>
       <c r="M126" s="21"/>
@@ -17390,7 +17385,7 @@
         <v>340</v>
       </c>
       <c r="I127" s="6"/>
-      <c r="J127" s="71"/>
+      <c r="J127" s="70"/>
       <c r="K127" s="19">
         <v>20</v>
       </c>
@@ -17513,7 +17508,7 @@
         <v>340</v>
       </c>
       <c r="I128" s="6"/>
-      <c r="J128" s="71"/>
+      <c r="J128" s="70"/>
       <c r="K128" s="19">
         <v>20</v>
       </c>
@@ -17632,7 +17627,7 @@
         <v>340</v>
       </c>
       <c r="I129" s="6"/>
-      <c r="J129" s="71"/>
+      <c r="J129" s="70"/>
       <c r="K129" s="21"/>
       <c r="L129" s="21"/>
       <c r="M129" s="21"/>
@@ -17747,7 +17742,7 @@
         <v>340</v>
       </c>
       <c r="I130" s="6"/>
-      <c r="J130" s="71"/>
+      <c r="J130" s="70"/>
       <c r="K130" s="19">
         <v>20</v>
       </c>
@@ -17872,7 +17867,7 @@
         <v>340</v>
       </c>
       <c r="I131" s="6"/>
-      <c r="J131" s="71"/>
+      <c r="J131" s="70"/>
       <c r="K131" s="19">
         <v>20</v>
       </c>
@@ -17991,7 +17986,7 @@
         <v>340</v>
       </c>
       <c r="I132" s="6"/>
-      <c r="J132" s="71"/>
+      <c r="J132" s="70"/>
       <c r="K132" s="21"/>
       <c r="L132" s="21"/>
       <c r="M132" s="21"/>
@@ -18110,7 +18105,7 @@
         <v>340</v>
       </c>
       <c r="I133" s="6"/>
-      <c r="J133" s="71"/>
+      <c r="J133" s="70"/>
       <c r="K133" s="19">
         <v>20</v>
       </c>
@@ -18231,7 +18226,7 @@
         <v>341</v>
       </c>
       <c r="I134" s="6"/>
-      <c r="J134" s="71"/>
+      <c r="J134" s="70"/>
       <c r="K134" s="21"/>
       <c r="L134" s="21"/>
       <c r="M134" s="21"/>
@@ -18348,7 +18343,7 @@
         <v>341</v>
       </c>
       <c r="I135" s="6"/>
-      <c r="J135" s="71"/>
+      <c r="J135" s="70"/>
       <c r="K135" s="19">
         <v>20</v>
       </c>
@@ -18473,7 +18468,7 @@
         <v>341</v>
       </c>
       <c r="I136" s="6"/>
-      <c r="J136" s="71"/>
+      <c r="J136" s="70"/>
       <c r="K136" s="19">
         <v>80</v>
       </c>
@@ -18594,7 +18589,7 @@
         <v>341</v>
       </c>
       <c r="I137" s="6"/>
-      <c r="J137" s="71"/>
+      <c r="J137" s="70"/>
       <c r="K137" s="21"/>
       <c r="L137" s="21"/>
       <c r="M137" s="21"/>
@@ -18709,7 +18704,7 @@
         <v>341</v>
       </c>
       <c r="I138" s="6"/>
-      <c r="J138" s="71"/>
+      <c r="J138" s="70"/>
       <c r="K138" s="19">
         <v>40</v>
       </c>
@@ -18830,7 +18825,7 @@
         <v>341</v>
       </c>
       <c r="I139" s="6"/>
-      <c r="J139" s="71"/>
+      <c r="J139" s="70"/>
       <c r="K139" s="21"/>
       <c r="L139" s="21"/>
       <c r="M139" s="21"/>
@@ -18949,7 +18944,7 @@
         <v>341</v>
       </c>
       <c r="I140" s="6"/>
-      <c r="J140" s="71"/>
+      <c r="J140" s="70"/>
       <c r="K140" s="21"/>
       <c r="L140" s="21"/>
       <c r="M140" s="21"/>
@@ -19066,7 +19061,7 @@
         <v>341</v>
       </c>
       <c r="I141" s="6"/>
-      <c r="J141" s="71"/>
+      <c r="J141" s="70"/>
       <c r="K141" s="19">
         <v>20</v>
       </c>
@@ -19191,7 +19186,7 @@
         <v>341</v>
       </c>
       <c r="I142" s="6"/>
-      <c r="J142" s="71"/>
+      <c r="J142" s="70"/>
       <c r="K142" s="19">
         <v>10</v>
       </c>
@@ -19312,7 +19307,7 @@
         <v>341</v>
       </c>
       <c r="I143" s="6"/>
-      <c r="J143" s="71"/>
+      <c r="J143" s="70"/>
       <c r="K143" s="19">
         <v>0</v>
       </c>
@@ -19437,7 +19432,7 @@
         <v>341</v>
       </c>
       <c r="I144" s="6"/>
-      <c r="J144" s="71"/>
+      <c r="J144" s="70"/>
       <c r="K144" s="19">
         <v>0</v>
       </c>
@@ -19554,7 +19549,7 @@
         <v>341</v>
       </c>
       <c r="I145" s="6"/>
-      <c r="J145" s="71"/>
+      <c r="J145" s="70"/>
       <c r="K145" s="19">
         <v>10</v>
       </c>
@@ -19675,7 +19670,7 @@
         <v>341</v>
       </c>
       <c r="I146" s="6"/>
-      <c r="J146" s="71"/>
+      <c r="J146" s="70"/>
       <c r="K146" s="21"/>
       <c r="L146" s="19">
         <v>10</v>
@@ -19796,7 +19791,7 @@
         <v>341</v>
       </c>
       <c r="I147" s="6"/>
-      <c r="J147" s="71"/>
+      <c r="J147" s="70"/>
       <c r="K147" s="19">
         <v>20</v>
       </c>
@@ -19921,7 +19916,7 @@
         <v>342</v>
       </c>
       <c r="I148" s="6"/>
-      <c r="J148" s="71"/>
+      <c r="J148" s="70"/>
       <c r="K148" s="19">
         <v>84</v>
       </c>
@@ -20044,7 +20039,7 @@
         <v>342</v>
       </c>
       <c r="I149" s="6"/>
-      <c r="J149" s="71"/>
+      <c r="J149" s="70"/>
       <c r="K149" s="19">
         <v>84</v>
       </c>
@@ -20165,7 +20160,7 @@
         <v>342</v>
       </c>
       <c r="I150" s="6"/>
-      <c r="J150" s="71"/>
+      <c r="J150" s="70"/>
       <c r="K150" s="21"/>
       <c r="L150" s="21"/>
       <c r="M150" s="21"/>
@@ -20282,7 +20277,7 @@
         <v>340</v>
       </c>
       <c r="I151" s="6"/>
-      <c r="J151" s="71"/>
+      <c r="J151" s="70"/>
       <c r="K151" s="21"/>
       <c r="L151" s="21"/>
       <c r="M151" s="21"/>
@@ -20401,7 +20396,7 @@
         <v>341</v>
       </c>
       <c r="I152" s="6"/>
-      <c r="J152" s="71"/>
+      <c r="J152" s="70"/>
       <c r="K152" s="21"/>
       <c r="L152" s="21"/>
       <c r="M152" s="21"/>
@@ -20518,7 +20513,7 @@
         <v>341</v>
       </c>
       <c r="I153" s="6"/>
-      <c r="J153" s="71"/>
+      <c r="J153" s="70"/>
       <c r="K153" s="21"/>
       <c r="L153" s="21"/>
       <c r="M153" s="21"/>
@@ -20637,7 +20632,7 @@
         <v>341</v>
       </c>
       <c r="I154" s="6"/>
-      <c r="J154" s="71"/>
+      <c r="J154" s="70"/>
       <c r="K154" s="21"/>
       <c r="L154" s="19">
         <v>20</v>
@@ -20760,7 +20755,7 @@
         <v>341</v>
       </c>
       <c r="I155" s="6"/>
-      <c r="J155" s="71"/>
+      <c r="J155" s="70"/>
       <c r="K155" s="19">
         <v>10</v>
       </c>
@@ -20879,7 +20874,7 @@
         <v>341</v>
       </c>
       <c r="I156" s="6"/>
-      <c r="J156" s="71"/>
+      <c r="J156" s="70"/>
       <c r="K156" s="19">
         <v>40</v>
       </c>
@@ -20998,7 +20993,7 @@
         <v>341</v>
       </c>
       <c r="I157" s="6"/>
-      <c r="J157" s="71"/>
+      <c r="J157" s="70"/>
       <c r="K157" s="21"/>
       <c r="L157" s="21"/>
       <c r="M157" s="21"/>
@@ -21117,7 +21112,7 @@
         <v>341</v>
       </c>
       <c r="I158" s="6"/>
-      <c r="J158" s="71"/>
+      <c r="J158" s="70"/>
       <c r="K158" s="21"/>
       <c r="L158" s="21"/>
       <c r="M158" s="21"/>
@@ -21236,7 +21231,7 @@
         <v>341</v>
       </c>
       <c r="I159" s="6"/>
-      <c r="J159" s="71"/>
+      <c r="J159" s="70"/>
       <c r="K159" s="21"/>
       <c r="L159" s="21"/>
       <c r="M159" s="21"/>
@@ -21355,7 +21350,7 @@
         <v>341</v>
       </c>
       <c r="I160" s="6"/>
-      <c r="J160" s="71"/>
+      <c r="J160" s="70"/>
       <c r="K160" s="21"/>
       <c r="L160" s="21"/>
       <c r="M160" s="21"/>
@@ -21474,7 +21469,7 @@
         <v>341</v>
       </c>
       <c r="I161" s="6"/>
-      <c r="J161" s="71"/>
+      <c r="J161" s="70"/>
       <c r="K161" s="19">
         <v>20</v>
       </c>
@@ -21593,7 +21588,7 @@
         <v>341</v>
       </c>
       <c r="I162" s="6"/>
-      <c r="J162" s="71"/>
+      <c r="J162" s="70"/>
       <c r="K162" s="19">
         <v>80</v>
       </c>
@@ -21718,7 +21713,7 @@
         <v>341</v>
       </c>
       <c r="I163" s="6"/>
-      <c r="J163" s="71"/>
+      <c r="J163" s="70"/>
       <c r="K163" s="21"/>
       <c r="L163" s="21"/>
       <c r="M163" s="21"/>
@@ -21837,7 +21832,7 @@
         <v>341</v>
       </c>
       <c r="I164" s="6"/>
-      <c r="J164" s="71"/>
+      <c r="J164" s="70"/>
       <c r="K164" s="21"/>
       <c r="L164" s="21"/>
       <c r="M164" s="21"/>
@@ -21954,7 +21949,7 @@
         <v>341</v>
       </c>
       <c r="I165" s="6"/>
-      <c r="J165" s="71"/>
+      <c r="J165" s="70"/>
       <c r="K165" s="21"/>
       <c r="L165" s="21"/>
       <c r="M165" s="21"/>
@@ -22073,7 +22068,7 @@
         <v>341</v>
       </c>
       <c r="I166" s="6"/>
-      <c r="J166" s="71"/>
+      <c r="J166" s="70"/>
       <c r="K166" s="21"/>
       <c r="L166" s="21"/>
       <c r="M166" s="21"/>
@@ -22192,7 +22187,7 @@
         <v>341</v>
       </c>
       <c r="I167" s="6"/>
-      <c r="J167" s="71"/>
+      <c r="J167" s="70"/>
       <c r="K167" s="19">
         <v>20</v>
       </c>
@@ -22309,7 +22304,7 @@
         <v>341</v>
       </c>
       <c r="I168" s="6"/>
-      <c r="J168" s="71"/>
+      <c r="J168" s="70"/>
       <c r="K168" s="21"/>
       <c r="L168" s="21"/>
       <c r="M168" s="21"/>
@@ -22428,7 +22423,7 @@
         <v>340</v>
       </c>
       <c r="I169" s="6"/>
-      <c r="J169" s="71"/>
+      <c r="J169" s="70"/>
       <c r="K169" s="21"/>
       <c r="L169" s="19">
         <v>20</v>
@@ -22551,7 +22546,7 @@
         <v>340</v>
       </c>
       <c r="I170" s="6"/>
-      <c r="J170" s="71"/>
+      <c r="J170" s="70"/>
       <c r="K170" s="19">
         <v>120</v>
       </c>
@@ -22670,7 +22665,7 @@
         <v>340</v>
       </c>
       <c r="I171" s="6"/>
-      <c r="J171" s="71"/>
+      <c r="J171" s="70"/>
       <c r="K171" s="19">
         <v>40</v>
       </c>
@@ -22789,7 +22784,7 @@
         <v>340</v>
       </c>
       <c r="I172" s="6"/>
-      <c r="J172" s="71"/>
+      <c r="J172" s="70"/>
       <c r="K172" s="19">
         <v>40</v>
       </c>
@@ -22914,7 +22909,7 @@
         <v>340</v>
       </c>
       <c r="I173" s="6"/>
-      <c r="J173" s="71"/>
+      <c r="J173" s="70"/>
       <c r="K173" s="21"/>
       <c r="L173" s="21"/>
       <c r="M173" s="21"/>
@@ -23033,7 +23028,7 @@
         <v>340</v>
       </c>
       <c r="I174" s="6"/>
-      <c r="J174" s="71"/>
+      <c r="J174" s="70"/>
       <c r="K174" s="19">
         <v>20</v>
       </c>
@@ -23158,7 +23153,7 @@
         <v>340</v>
       </c>
       <c r="I175" s="6"/>
-      <c r="J175" s="71"/>
+      <c r="J175" s="70"/>
       <c r="K175" s="19">
         <v>20</v>
       </c>
@@ -23283,7 +23278,7 @@
         <v>340</v>
       </c>
       <c r="I176" s="6"/>
-      <c r="J176" s="71"/>
+      <c r="J176" s="70"/>
       <c r="K176" s="19">
         <v>20</v>
       </c>
@@ -23408,7 +23403,7 @@
         <v>339</v>
       </c>
       <c r="I177" s="6"/>
-      <c r="J177" s="71"/>
+      <c r="J177" s="70"/>
       <c r="K177" s="19">
         <v>40</v>
       </c>
@@ -23533,7 +23528,7 @@
         <v>342</v>
       </c>
       <c r="I178" s="6"/>
-      <c r="J178" s="71"/>
+      <c r="J178" s="70"/>
       <c r="K178" s="21"/>
       <c r="L178" s="21"/>
       <c r="M178" s="21"/>
@@ -23652,7 +23647,7 @@
         <v>341</v>
       </c>
       <c r="I179" s="6"/>
-      <c r="J179" s="71"/>
+      <c r="J179" s="70"/>
       <c r="K179" s="19">
         <v>10</v>
       </c>
@@ -23777,7 +23772,7 @@
         <v>341</v>
       </c>
       <c r="I180" s="6"/>
-      <c r="J180" s="71"/>
+      <c r="J180" s="70"/>
       <c r="K180" s="19">
         <v>40</v>
       </c>
@@ -23900,7 +23895,7 @@
         <v>341</v>
       </c>
       <c r="I181" s="6"/>
-      <c r="J181" s="71"/>
+      <c r="J181" s="70"/>
       <c r="K181" s="21"/>
       <c r="L181" s="21"/>
       <c r="M181" s="21"/>
@@ -24019,7 +24014,7 @@
         <v>341</v>
       </c>
       <c r="I182" s="6"/>
-      <c r="J182" s="71"/>
+      <c r="J182" s="70"/>
       <c r="K182" s="19">
         <v>10</v>
       </c>
@@ -24138,7 +24133,7 @@
         <v>341</v>
       </c>
       <c r="I183" s="6"/>
-      <c r="J183" s="71"/>
+      <c r="J183" s="70"/>
       <c r="K183" s="21"/>
       <c r="L183" s="21"/>
       <c r="M183" s="21"/>
@@ -24257,7 +24252,7 @@
         <v>341</v>
       </c>
       <c r="I184" s="6"/>
-      <c r="J184" s="71"/>
+      <c r="J184" s="70"/>
       <c r="K184" s="19">
         <v>20</v>
       </c>
@@ -24382,7 +24377,7 @@
         <v>341</v>
       </c>
       <c r="I185" s="6"/>
-      <c r="J185" s="71"/>
+      <c r="J185" s="70"/>
       <c r="K185" s="21"/>
       <c r="L185" s="21"/>
       <c r="M185" s="21"/>
@@ -24501,7 +24496,7 @@
         <v>341</v>
       </c>
       <c r="I186" s="6"/>
-      <c r="J186" s="71"/>
+      <c r="J186" s="70"/>
       <c r="K186" s="21"/>
       <c r="L186" s="21"/>
       <c r="M186" s="21"/>
@@ -24618,7 +24613,7 @@
         <v>341</v>
       </c>
       <c r="I187" s="6"/>
-      <c r="J187" s="71"/>
+      <c r="J187" s="70"/>
       <c r="K187" s="19">
         <v>20</v>
       </c>
@@ -24743,7 +24738,7 @@
         <v>341</v>
       </c>
       <c r="I188" s="6"/>
-      <c r="J188" s="71"/>
+      <c r="J188" s="70"/>
       <c r="K188" s="21"/>
       <c r="L188" s="19">
         <v>40</v>
@@ -24866,7 +24861,7 @@
         <v>341</v>
       </c>
       <c r="I189" s="6"/>
-      <c r="J189" s="71"/>
+      <c r="J189" s="70"/>
       <c r="K189" s="21"/>
       <c r="L189" s="21"/>
       <c r="M189" s="21"/>
@@ -24985,7 +24980,7 @@
         <v>341</v>
       </c>
       <c r="I190" s="6"/>
-      <c r="J190" s="71"/>
+      <c r="J190" s="70"/>
       <c r="K190" s="21"/>
       <c r="L190" s="21"/>
       <c r="M190" s="21"/>
@@ -25104,7 +25099,7 @@
         <v>341</v>
       </c>
       <c r="I191" s="6"/>
-      <c r="J191" s="71"/>
+      <c r="J191" s="70"/>
       <c r="K191" s="21"/>
       <c r="L191" s="21"/>
       <c r="M191" s="21"/>
@@ -25223,7 +25218,7 @@
         <v>341</v>
       </c>
       <c r="I192" s="6"/>
-      <c r="J192" s="71"/>
+      <c r="J192" s="70"/>
       <c r="K192" s="21"/>
       <c r="L192" s="21"/>
       <c r="M192" s="21"/>
@@ -25342,7 +25337,7 @@
         <v>341</v>
       </c>
       <c r="I193" s="6"/>
-      <c r="J193" s="71"/>
+      <c r="J193" s="70"/>
       <c r="K193" s="19">
         <v>20</v>
       </c>
@@ -25467,7 +25462,7 @@
         <v>341</v>
       </c>
       <c r="I194" s="6"/>
-      <c r="J194" s="71"/>
+      <c r="J194" s="70"/>
       <c r="K194" s="21"/>
       <c r="L194" s="21"/>
       <c r="M194" s="21"/>
@@ -25584,7 +25579,7 @@
         <v>341</v>
       </c>
       <c r="I195" s="6"/>
-      <c r="J195" s="71"/>
+      <c r="J195" s="70"/>
       <c r="K195" s="21"/>
       <c r="L195" s="21"/>
       <c r="M195" s="21"/>
@@ -25703,7 +25698,7 @@
         <v>342</v>
       </c>
       <c r="I196" s="6"/>
-      <c r="J196" s="71"/>
+      <c r="J196" s="70"/>
       <c r="K196" s="19">
         <v>120</v>
       </c>
@@ -25828,7 +25823,7 @@
         <v>342</v>
       </c>
       <c r="I197" s="6"/>
-      <c r="J197" s="71"/>
+      <c r="J197" s="70"/>
       <c r="K197" s="19">
         <v>40</v>
       </c>
@@ -25953,7 +25948,7 @@
         <v>341</v>
       </c>
       <c r="I198" s="6"/>
-      <c r="J198" s="71"/>
+      <c r="J198" s="70"/>
       <c r="K198" s="21"/>
       <c r="L198" s="21"/>
       <c r="M198" s="21"/>
@@ -26070,7 +26065,7 @@
         <v>341</v>
       </c>
       <c r="I199" s="6"/>
-      <c r="J199" s="71"/>
+      <c r="J199" s="70"/>
       <c r="K199" s="21"/>
       <c r="L199" s="21"/>
       <c r="M199" s="21"/>
@@ -26189,7 +26184,7 @@
         <v>341</v>
       </c>
       <c r="I200" s="6"/>
-      <c r="J200" s="71"/>
+      <c r="J200" s="70"/>
       <c r="K200" s="21"/>
       <c r="L200" s="21"/>
       <c r="M200" s="21"/>
@@ -26304,7 +26299,7 @@
         <v>341</v>
       </c>
       <c r="I201" s="6"/>
-      <c r="J201" s="71"/>
+      <c r="J201" s="70"/>
       <c r="K201" s="21"/>
       <c r="L201" s="21"/>
       <c r="M201" s="21"/>
@@ -26423,7 +26418,7 @@
         <v>341</v>
       </c>
       <c r="I202" s="6"/>
-      <c r="J202" s="71"/>
+      <c r="J202" s="70"/>
       <c r="K202" s="19">
         <v>20</v>
       </c>
@@ -26540,7 +26535,7 @@
         <v>341</v>
       </c>
       <c r="I203" s="6"/>
-      <c r="J203" s="71"/>
+      <c r="J203" s="70"/>
       <c r="K203" s="21"/>
       <c r="L203" s="19">
         <v>20</v>
@@ -26657,7 +26652,7 @@
         <v>341</v>
       </c>
       <c r="I204" s="6"/>
-      <c r="J204" s="71"/>
+      <c r="J204" s="70"/>
       <c r="K204" s="19">
         <v>20</v>
       </c>
@@ -26776,7 +26771,7 @@
         <v>341</v>
       </c>
       <c r="I205" s="6"/>
-      <c r="J205" s="71"/>
+      <c r="J205" s="70"/>
       <c r="K205" s="21"/>
       <c r="L205" s="21"/>
       <c r="M205" s="21"/>
@@ -26895,7 +26890,7 @@
         <v>341</v>
       </c>
       <c r="I206" s="6"/>
-      <c r="J206" s="71"/>
+      <c r="J206" s="70"/>
       <c r="K206" s="19">
         <v>10</v>
       </c>
@@ -27014,7 +27009,7 @@
         <v>341</v>
       </c>
       <c r="I207" s="6"/>
-      <c r="J207" s="71"/>
+      <c r="J207" s="70"/>
       <c r="K207" s="21"/>
       <c r="L207" s="21"/>
       <c r="M207" s="21"/>
@@ -27131,7 +27126,7 @@
         <v>341</v>
       </c>
       <c r="I208" s="6"/>
-      <c r="J208" s="71"/>
+      <c r="J208" s="70"/>
       <c r="K208" s="19">
         <v>40</v>
       </c>
@@ -27256,7 +27251,7 @@
         <v>341</v>
       </c>
       <c r="I209" s="6"/>
-      <c r="J209" s="71"/>
+      <c r="J209" s="70"/>
       <c r="K209" s="21"/>
       <c r="L209" s="21"/>
       <c r="M209" s="21"/>
@@ -27375,7 +27370,7 @@
         <v>340</v>
       </c>
       <c r="I210" s="6"/>
-      <c r="J210" s="71"/>
+      <c r="J210" s="70"/>
       <c r="K210" s="21"/>
       <c r="L210" s="21"/>
       <c r="M210" s="21"/>
@@ -27492,7 +27487,7 @@
         <v>341</v>
       </c>
       <c r="I211" s="6"/>
-      <c r="J211" s="71"/>
+      <c r="J211" s="70"/>
       <c r="K211" s="21"/>
       <c r="L211" s="21"/>
       <c r="M211" s="21"/>
@@ -27611,7 +27606,7 @@
         <v>340</v>
       </c>
       <c r="I212" s="6"/>
-      <c r="J212" s="71"/>
+      <c r="J212" s="70"/>
       <c r="K212" s="21"/>
       <c r="L212" s="21"/>
       <c r="M212" s="21"/>
@@ -27730,7 +27725,7 @@
         <v>341</v>
       </c>
       <c r="I213" s="6"/>
-      <c r="J213" s="71"/>
+      <c r="J213" s="70"/>
       <c r="K213" s="21"/>
       <c r="L213" s="21"/>
       <c r="M213" s="21"/>
@@ -27847,7 +27842,7 @@
         <v>342</v>
       </c>
       <c r="I214" s="6"/>
-      <c r="J214" s="71"/>
+      <c r="J214" s="70"/>
       <c r="K214" s="19">
         <v>40</v>
       </c>
@@ -27972,7 +27967,7 @@
         <v>341</v>
       </c>
       <c r="I215" s="6"/>
-      <c r="J215" s="71"/>
+      <c r="J215" s="70"/>
       <c r="K215" s="21"/>
       <c r="L215" s="21"/>
       <c r="M215" s="21"/>
@@ -28087,7 +28082,7 @@
         <v>342</v>
       </c>
       <c r="I216" s="6"/>
-      <c r="J216" s="71"/>
+      <c r="J216" s="70"/>
       <c r="K216" s="19">
         <v>105</v>
       </c>
@@ -28210,7 +28205,7 @@
         <v>342</v>
       </c>
       <c r="I217" s="6"/>
-      <c r="J217" s="71"/>
+      <c r="J217" s="70"/>
       <c r="K217" s="21"/>
       <c r="L217" s="21"/>
       <c r="M217" s="21"/>
@@ -28325,7 +28320,7 @@
         <v>342</v>
       </c>
       <c r="I218" s="6"/>
-      <c r="J218" s="71"/>
+      <c r="J218" s="70"/>
       <c r="K218" s="19">
         <v>168</v>
       </c>
@@ -28448,7 +28443,7 @@
         <v>342</v>
       </c>
       <c r="I219" s="6"/>
-      <c r="J219" s="71"/>
+      <c r="J219" s="70"/>
       <c r="K219" s="21"/>
       <c r="L219" s="19">
         <v>2</v>
@@ -28565,7 +28560,7 @@
         <v>341</v>
       </c>
       <c r="I220" s="6"/>
-      <c r="J220" s="71"/>
+      <c r="J220" s="70"/>
       <c r="K220" s="21"/>
       <c r="L220" s="21"/>
       <c r="M220" s="21"/>
@@ -28684,7 +28679,7 @@
         <v>341</v>
       </c>
       <c r="I221" s="6"/>
-      <c r="J221" s="71"/>
+      <c r="J221" s="70"/>
       <c r="K221" s="21"/>
       <c r="L221" s="21"/>
       <c r="M221" s="21"/>
@@ -28799,7 +28794,7 @@
         <v>341</v>
       </c>
       <c r="I222" s="6"/>
-      <c r="J222" s="71"/>
+      <c r="J222" s="70"/>
       <c r="K222" s="21"/>
       <c r="L222" s="21"/>
       <c r="M222" s="21"/>
@@ -28918,7 +28913,7 @@
         <v>341</v>
       </c>
       <c r="I223" s="6"/>
-      <c r="J223" s="71"/>
+      <c r="J223" s="70"/>
       <c r="K223" s="21"/>
       <c r="L223" s="21"/>
       <c r="M223" s="21"/>
@@ -29037,7 +29032,7 @@
         <v>341</v>
       </c>
       <c r="I224" s="6"/>
-      <c r="J224" s="71"/>
+      <c r="J224" s="70"/>
       <c r="K224" s="21"/>
       <c r="L224" s="21"/>
       <c r="M224" s="21"/>
@@ -29156,7 +29151,7 @@
         <v>341</v>
       </c>
       <c r="I225" s="6"/>
-      <c r="J225" s="71"/>
+      <c r="J225" s="70"/>
       <c r="K225" s="19">
         <v>40</v>
       </c>
@@ -29275,7 +29270,7 @@
         <v>341</v>
       </c>
       <c r="I226" s="6"/>
-      <c r="J226" s="71"/>
+      <c r="J226" s="70"/>
       <c r="K226" s="19">
         <v>20</v>
       </c>
@@ -29400,7 +29395,7 @@
         <v>341</v>
       </c>
       <c r="I227" s="6"/>
-      <c r="J227" s="71"/>
+      <c r="J227" s="70"/>
       <c r="K227" s="19">
         <v>20</v>
       </c>
@@ -29523,7 +29518,7 @@
         <v>341</v>
       </c>
       <c r="I228" s="6"/>
-      <c r="J228" s="71"/>
+      <c r="J228" s="70"/>
       <c r="K228" s="21"/>
       <c r="L228" s="21"/>
       <c r="M228" s="21"/>
@@ -29640,7 +29635,7 @@
         <v>341</v>
       </c>
       <c r="I229" s="6"/>
-      <c r="J229" s="71"/>
+      <c r="J229" s="70"/>
       <c r="K229" s="21"/>
       <c r="L229" s="21"/>
       <c r="M229" s="21"/>
@@ -29757,7 +29752,7 @@
         <v>342</v>
       </c>
       <c r="I230" s="6"/>
-      <c r="J230" s="71"/>
+      <c r="J230" s="70"/>
       <c r="K230" s="21"/>
       <c r="L230" s="21"/>
       <c r="M230" s="21"/>
@@ -29874,7 +29869,7 @@
         <v>341</v>
       </c>
       <c r="I231" s="6"/>
-      <c r="J231" s="71"/>
+      <c r="J231" s="70"/>
       <c r="K231" s="19">
         <v>20</v>
       </c>
@@ -29999,7 +29994,7 @@
         <v>340</v>
       </c>
       <c r="I232" s="6"/>
-      <c r="J232" s="71"/>
+      <c r="J232" s="70"/>
       <c r="K232" s="19">
         <v>20</v>
       </c>
@@ -30122,7 +30117,7 @@
         <v>340</v>
       </c>
       <c r="I233" s="6"/>
-      <c r="J233" s="71"/>
+      <c r="J233" s="70"/>
       <c r="K233" s="21"/>
       <c r="L233" s="21"/>
       <c r="M233" s="21"/>
@@ -30241,7 +30236,7 @@
         <v>342</v>
       </c>
       <c r="I234" s="6"/>
-      <c r="J234" s="71"/>
+      <c r="J234" s="70"/>
       <c r="K234" s="19">
         <v>1</v>
       </c>
@@ -30364,7 +30359,7 @@
         <v>342</v>
       </c>
       <c r="I235" s="6"/>
-      <c r="J235" s="71"/>
+      <c r="J235" s="70"/>
       <c r="K235" s="19">
         <v>160</v>
       </c>
@@ -30489,7 +30484,7 @@
         <v>340</v>
       </c>
       <c r="I236" s="6"/>
-      <c r="J236" s="71"/>
+      <c r="J236" s="70"/>
       <c r="K236" s="19">
         <v>20</v>
       </c>
@@ -30608,7 +30603,7 @@
         <v>340</v>
       </c>
       <c r="I237" s="6"/>
-      <c r="J237" s="71"/>
+      <c r="J237" s="70"/>
       <c r="K237" s="19">
         <v>20</v>
       </c>
@@ -30727,7 +30722,7 @@
         <v>340</v>
       </c>
       <c r="I238" s="6"/>
-      <c r="J238" s="71"/>
+      <c r="J238" s="70"/>
       <c r="K238" s="19">
         <v>0</v>
       </c>
@@ -30852,7 +30847,7 @@
         <v>340</v>
       </c>
       <c r="I239" s="6"/>
-      <c r="J239" s="71"/>
+      <c r="J239" s="70"/>
       <c r="K239" s="21"/>
       <c r="L239" s="19">
         <v>20</v>
@@ -30969,7 +30964,7 @@
         <v>340</v>
       </c>
       <c r="I240" s="6"/>
-      <c r="J240" s="71"/>
+      <c r="J240" s="70"/>
       <c r="K240" s="21"/>
       <c r="L240" s="19">
         <v>20</v>
@@ -31092,7 +31087,7 @@
         <v>340</v>
       </c>
       <c r="I241" s="6"/>
-      <c r="J241" s="71"/>
+      <c r="J241" s="70"/>
       <c r="K241" s="19">
         <v>20</v>
       </c>
@@ -31211,7 +31206,7 @@
         <v>340</v>
       </c>
       <c r="I242" s="6"/>
-      <c r="J242" s="71"/>
+      <c r="J242" s="70"/>
       <c r="K242" s="19">
         <v>10</v>
       </c>
@@ -31330,7 +31325,7 @@
         <v>340</v>
       </c>
       <c r="I243" s="6"/>
-      <c r="J243" s="71"/>
+      <c r="J243" s="70"/>
       <c r="K243" s="19">
         <v>0</v>
       </c>
@@ -31455,7 +31450,7 @@
         <v>340</v>
       </c>
       <c r="I244" s="6"/>
-      <c r="J244" s="71"/>
+      <c r="J244" s="70"/>
       <c r="K244" s="19">
         <v>20</v>
       </c>
@@ -31580,7 +31575,7 @@
         <v>339</v>
       </c>
       <c r="I245" s="6"/>
-      <c r="J245" s="71"/>
+      <c r="J245" s="70"/>
       <c r="K245" s="19">
         <v>10</v>
       </c>
@@ -31699,7 +31694,7 @@
         <v>339</v>
       </c>
       <c r="I246" s="6"/>
-      <c r="J246" s="71"/>
+      <c r="J246" s="70"/>
       <c r="K246" s="19">
         <v>20</v>
       </c>
@@ -31824,7 +31819,7 @@
         <v>339</v>
       </c>
       <c r="I247" s="6"/>
-      <c r="J247" s="71"/>
+      <c r="J247" s="70"/>
       <c r="K247" s="19">
         <v>10</v>
       </c>
@@ -31949,7 +31944,7 @@
         <v>339</v>
       </c>
       <c r="I248" s="6"/>
-      <c r="J248" s="71"/>
+      <c r="J248" s="70"/>
       <c r="K248" s="19">
         <v>20</v>
       </c>
@@ -32072,7 +32067,7 @@
         <v>339</v>
       </c>
       <c r="I249" s="6"/>
-      <c r="J249" s="71"/>
+      <c r="J249" s="70"/>
       <c r="K249" s="19">
         <v>20</v>
       </c>
@@ -32197,7 +32192,7 @@
         <v>339</v>
       </c>
       <c r="I250" s="6"/>
-      <c r="J250" s="71"/>
+      <c r="J250" s="70"/>
       <c r="K250" s="19">
         <v>20</v>
       </c>
@@ -32322,7 +32317,7 @@
         <v>342</v>
       </c>
       <c r="I251" s="6"/>
-      <c r="J251" s="71"/>
+      <c r="J251" s="70"/>
       <c r="K251" s="19">
         <v>-40</v>
       </c>
@@ -32445,7 +32440,7 @@
         <v>342</v>
       </c>
       <c r="I252" s="6"/>
-      <c r="J252" s="71"/>
+      <c r="J252" s="70"/>
       <c r="K252" s="21"/>
       <c r="L252" s="21"/>
       <c r="M252" s="21"/>
@@ -32560,7 +32555,7 @@
         <v>340</v>
       </c>
       <c r="I253" s="6"/>
-      <c r="J253" s="71"/>
+      <c r="J253" s="70"/>
       <c r="K253" s="21"/>
       <c r="L253" s="21"/>
       <c r="M253" s="21"/>
@@ -32675,7 +32670,7 @@
         <v>340</v>
       </c>
       <c r="I254" s="6"/>
-      <c r="J254" s="71"/>
+      <c r="J254" s="70"/>
       <c r="K254" s="19">
         <v>20</v>
       </c>
@@ -32790,7 +32785,7 @@
         <v>340</v>
       </c>
       <c r="I255" s="6"/>
-      <c r="J255" s="71"/>
+      <c r="J255" s="70"/>
       <c r="K255" s="21"/>
       <c r="L255" s="21"/>
       <c r="M255" s="21"/>
@@ -32909,7 +32904,7 @@
         <v>340</v>
       </c>
       <c r="I256" s="6"/>
-      <c r="J256" s="71"/>
+      <c r="J256" s="70"/>
       <c r="K256" s="19">
         <v>10</v>
       </c>
@@ -33034,7 +33029,7 @@
         <v>341</v>
       </c>
       <c r="I257" s="6"/>
-      <c r="J257" s="71"/>
+      <c r="J257" s="70"/>
       <c r="K257" s="21"/>
       <c r="L257" s="21"/>
       <c r="M257" s="21"/>
@@ -33151,7 +33146,7 @@
         <v>341</v>
       </c>
       <c r="I258" s="6"/>
-      <c r="J258" s="71"/>
+      <c r="J258" s="70"/>
       <c r="K258" s="19">
         <v>10</v>
       </c>
@@ -33268,7 +33263,7 @@
         <v>341</v>
       </c>
       <c r="I259" s="6"/>
-      <c r="J259" s="71"/>
+      <c r="J259" s="70"/>
       <c r="K259" s="19">
         <v>10</v>
       </c>
@@ -33385,7 +33380,7 @@
         <v>341</v>
       </c>
       <c r="I260" s="6"/>
-      <c r="J260" s="71"/>
+      <c r="J260" s="70"/>
       <c r="K260" s="21"/>
       <c r="L260" s="19">
         <v>20</v>
@@ -33502,7 +33497,7 @@
         <v>341</v>
       </c>
       <c r="I261" s="6"/>
-      <c r="J261" s="71"/>
+      <c r="J261" s="70"/>
       <c r="K261" s="19">
         <v>40</v>
       </c>
@@ -33619,7 +33614,7 @@
         <v>341</v>
       </c>
       <c r="I262" s="6"/>
-      <c r="J262" s="71"/>
+      <c r="J262" s="70"/>
       <c r="K262" s="21"/>
       <c r="L262" s="21"/>
       <c r="M262" s="21"/>
@@ -33738,7 +33733,7 @@
         <v>341</v>
       </c>
       <c r="I263" s="6"/>
-      <c r="J263" s="71"/>
+      <c r="J263" s="70"/>
       <c r="K263" s="21"/>
       <c r="L263" s="21"/>
       <c r="M263" s="21"/>
@@ -33857,7 +33852,7 @@
         <v>341</v>
       </c>
       <c r="I264" s="6"/>
-      <c r="J264" s="71"/>
+      <c r="J264" s="70"/>
       <c r="K264" s="21"/>
       <c r="L264" s="21"/>
       <c r="M264" s="19">
@@ -33976,7 +33971,7 @@
         <v>341</v>
       </c>
       <c r="I265" s="6"/>
-      <c r="J265" s="71"/>
+      <c r="J265" s="70"/>
       <c r="K265" s="19">
         <v>20</v>
       </c>
@@ -34101,7 +34096,7 @@
         <v>341</v>
       </c>
       <c r="I266" s="6"/>
-      <c r="J266" s="71"/>
+      <c r="J266" s="70"/>
       <c r="K266" s="21"/>
       <c r="L266" s="21"/>
       <c r="M266" s="21"/>
@@ -34220,7 +34215,7 @@
         <v>339</v>
       </c>
       <c r="I267" s="6"/>
-      <c r="J267" s="71"/>
+      <c r="J267" s="70"/>
       <c r="K267" s="19">
         <v>20</v>
       </c>
@@ -34345,7 +34340,7 @@
         <v>339</v>
       </c>
       <c r="I268" s="6"/>
-      <c r="J268" s="71"/>
+      <c r="J268" s="70"/>
       <c r="K268" s="19">
         <v>10</v>
       </c>
@@ -34464,7 +34459,7 @@
         <v>339</v>
       </c>
       <c r="I269" s="6"/>
-      <c r="J269" s="71"/>
+      <c r="J269" s="70"/>
       <c r="K269" s="19">
         <v>20</v>
       </c>
@@ -34581,7 +34576,7 @@
         <v>339</v>
       </c>
       <c r="I270" s="6"/>
-      <c r="J270" s="71"/>
+      <c r="J270" s="70"/>
       <c r="K270" s="19">
         <v>40</v>
       </c>
@@ -34700,7 +34695,7 @@
         <v>339</v>
       </c>
       <c r="I271" s="6"/>
-      <c r="J271" s="71"/>
+      <c r="J271" s="70"/>
       <c r="K271" s="19">
         <v>20</v>
       </c>
@@ -34825,7 +34820,7 @@
         <v>339</v>
       </c>
       <c r="I272" s="6"/>
-      <c r="J272" s="71"/>
+      <c r="J272" s="70"/>
       <c r="K272" s="21"/>
       <c r="L272" s="21"/>
       <c r="M272" s="21"/>
@@ -34942,7 +34937,7 @@
         <v>339</v>
       </c>
       <c r="I273" s="6"/>
-      <c r="J273" s="71"/>
+      <c r="J273" s="70"/>
       <c r="K273" s="19">
         <v>20</v>
       </c>
@@ -35067,7 +35062,7 @@
         <v>339</v>
       </c>
       <c r="I274" s="6"/>
-      <c r="J274" s="71"/>
+      <c r="J274" s="70"/>
       <c r="K274" s="21"/>
       <c r="L274" s="21"/>
       <c r="M274" s="21"/>
@@ -35186,7 +35181,7 @@
         <v>339</v>
       </c>
       <c r="I275" s="6"/>
-      <c r="J275" s="71"/>
+      <c r="J275" s="70"/>
       <c r="K275" s="19">
         <v>10</v>
       </c>
@@ -35305,7 +35300,7 @@
         <v>339</v>
       </c>
       <c r="I276" s="6"/>
-      <c r="J276" s="71"/>
+      <c r="J276" s="70"/>
       <c r="K276" s="19">
         <v>40</v>
       </c>
@@ -35426,7 +35421,7 @@
         <v>339</v>
       </c>
       <c r="I277" s="6"/>
-      <c r="J277" s="71"/>
+      <c r="J277" s="70"/>
       <c r="K277" s="19">
         <v>10</v>
       </c>
@@ -35551,7 +35546,7 @@
         <v>339</v>
       </c>
       <c r="I278" s="6"/>
-      <c r="J278" s="71"/>
+      <c r="J278" s="70"/>
       <c r="K278" s="19">
         <v>10</v>
       </c>
@@ -35672,7 +35667,7 @@
         <v>339</v>
       </c>
       <c r="I279" s="6"/>
-      <c r="J279" s="71"/>
+      <c r="J279" s="70"/>
       <c r="K279" s="19">
         <v>20</v>
       </c>
@@ -35797,7 +35792,7 @@
         <v>339</v>
       </c>
       <c r="I280" s="6"/>
-      <c r="J280" s="71"/>
+      <c r="J280" s="70"/>
       <c r="K280" s="19">
         <v>10</v>
       </c>
@@ -35914,7 +35909,7 @@
         <v>339</v>
       </c>
       <c r="I281" s="6"/>
-      <c r="J281" s="71"/>
+      <c r="J281" s="70"/>
       <c r="K281" s="19">
         <v>20</v>
       </c>
@@ -36037,7 +36032,7 @@
         <v>339</v>
       </c>
       <c r="I282" s="6"/>
-      <c r="J282" s="71"/>
+      <c r="J282" s="70"/>
       <c r="K282" s="19">
         <v>20</v>
       </c>
@@ -36162,7 +36157,7 @@
         <v>339</v>
       </c>
       <c r="I283" s="6"/>
-      <c r="J283" s="71"/>
+      <c r="J283" s="70"/>
       <c r="K283" s="19">
         <v>40</v>
       </c>
@@ -36287,7 +36282,7 @@
         <v>339</v>
       </c>
       <c r="I284" s="6"/>
-      <c r="J284" s="71"/>
+      <c r="J284" s="70"/>
       <c r="K284" s="19">
         <v>40</v>
       </c>
@@ -36412,7 +36407,7 @@
         <v>339</v>
       </c>
       <c r="I285" s="6"/>
-      <c r="J285" s="71"/>
+      <c r="J285" s="70"/>
       <c r="K285" s="19">
         <v>10</v>
       </c>
@@ -36537,7 +36532,7 @@
         <v>339</v>
       </c>
       <c r="I286" s="6"/>
-      <c r="J286" s="71"/>
+      <c r="J286" s="70"/>
       <c r="K286" s="21"/>
       <c r="L286" s="21"/>
       <c r="M286" s="21"/>
@@ -36656,7 +36651,7 @@
         <v>339</v>
       </c>
       <c r="I287" s="6"/>
-      <c r="J287" s="71"/>
+      <c r="J287" s="70"/>
       <c r="K287" s="21"/>
       <c r="L287" s="21"/>
       <c r="M287" s="21"/>
@@ -36775,7 +36770,7 @@
         <v>339</v>
       </c>
       <c r="I288" s="6"/>
-      <c r="J288" s="71"/>
+      <c r="J288" s="70"/>
       <c r="K288" s="21"/>
       <c r="L288" s="21"/>
       <c r="M288" s="21"/>
@@ -36894,7 +36889,7 @@
         <v>339</v>
       </c>
       <c r="I289" s="6"/>
-      <c r="J289" s="71"/>
+      <c r="J289" s="70"/>
       <c r="K289" s="19">
         <v>0</v>
       </c>
@@ -37013,7 +37008,7 @@
         <v>340</v>
       </c>
       <c r="I290" s="6"/>
-      <c r="J290" s="71"/>
+      <c r="J290" s="70"/>
       <c r="K290" s="19">
         <v>20</v>
       </c>
@@ -37138,7 +37133,7 @@
         <v>340</v>
       </c>
       <c r="I291" s="6"/>
-      <c r="J291" s="71"/>
+      <c r="J291" s="70"/>
       <c r="K291" s="19">
         <v>40</v>
       </c>
@@ -37261,7 +37256,7 @@
         <v>340</v>
       </c>
       <c r="I292" s="6"/>
-      <c r="J292" s="71"/>
+      <c r="J292" s="70"/>
       <c r="K292" s="21"/>
       <c r="L292" s="21"/>
       <c r="M292" s="21"/>
@@ -37380,7 +37375,7 @@
         <v>340</v>
       </c>
       <c r="I293" s="6"/>
-      <c r="J293" s="71"/>
+      <c r="J293" s="70"/>
       <c r="K293" s="21"/>
       <c r="L293" s="21"/>
       <c r="M293" s="21"/>
@@ -37499,7 +37494,7 @@
         <v>340</v>
       </c>
       <c r="I294" s="6"/>
-      <c r="J294" s="71"/>
+      <c r="J294" s="70"/>
       <c r="K294" s="19">
         <v>20</v>
       </c>
@@ -37618,7 +37613,7 @@
         <v>340</v>
       </c>
       <c r="I295" s="6"/>
-      <c r="J295" s="71"/>
+      <c r="J295" s="70"/>
       <c r="K295" s="19">
         <v>20</v>
       </c>
@@ -37743,7 +37738,7 @@
         <v>340</v>
       </c>
       <c r="I296" s="6"/>
-      <c r="J296" s="71"/>
+      <c r="J296" s="70"/>
       <c r="K296" s="19">
         <v>20</v>
       </c>
@@ -37868,7 +37863,7 @@
         <v>340</v>
       </c>
       <c r="I297" s="6"/>
-      <c r="J297" s="71"/>
+      <c r="J297" s="70"/>
       <c r="K297" s="21"/>
       <c r="L297" s="21"/>
       <c r="M297" s="21"/>
@@ -37987,7 +37982,7 @@
         <v>340</v>
       </c>
       <c r="I298" s="6"/>
-      <c r="J298" s="71"/>
+      <c r="J298" s="70"/>
       <c r="K298" s="21"/>
       <c r="L298" s="21"/>
       <c r="M298" s="21"/>
@@ -38106,7 +38101,7 @@
         <v>342</v>
       </c>
       <c r="I299" s="6"/>
-      <c r="J299" s="71"/>
+      <c r="J299" s="70"/>
       <c r="K299" s="19">
         <v>80</v>
       </c>
@@ -38231,7 +38226,7 @@
         <v>342</v>
       </c>
       <c r="I300" s="6"/>
-      <c r="J300" s="71"/>
+      <c r="J300" s="70"/>
       <c r="K300" s="19">
         <v>40</v>
       </c>
@@ -38356,7 +38351,7 @@
         <v>342</v>
       </c>
       <c r="I301" s="6"/>
-      <c r="J301" s="71"/>
+      <c r="J301" s="70"/>
       <c r="K301" s="21"/>
       <c r="L301" s="21"/>
       <c r="M301" s="21"/>
@@ -38475,7 +38470,7 @@
         <v>342</v>
       </c>
       <c r="I302" s="6"/>
-      <c r="J302" s="71"/>
+      <c r="J302" s="70"/>
       <c r="K302" s="19">
         <v>40</v>
       </c>
@@ -38600,7 +38595,7 @@
         <v>342</v>
       </c>
       <c r="I303" s="6"/>
-      <c r="J303" s="71"/>
+      <c r="J303" s="70"/>
       <c r="K303" s="21"/>
       <c r="L303" s="21"/>
       <c r="M303" s="19">
@@ -38721,7 +38716,7 @@
         <v>339</v>
       </c>
       <c r="I304" s="6"/>
-      <c r="J304" s="71"/>
+      <c r="J304" s="70"/>
       <c r="K304" s="19">
         <v>20</v>
       </c>
@@ -38846,7 +38841,7 @@
         <v>339</v>
       </c>
       <c r="I305" s="6"/>
-      <c r="J305" s="71"/>
+      <c r="J305" s="70"/>
       <c r="K305" s="21"/>
       <c r="L305" s="21"/>
       <c r="M305" s="21"/>
@@ -38965,7 +38960,7 @@
         <v>339</v>
       </c>
       <c r="I306" s="6"/>
-      <c r="J306" s="71"/>
+      <c r="J306" s="70"/>
       <c r="K306" s="21"/>
       <c r="L306" s="21"/>
       <c r="M306" s="21"/>
@@ -39084,7 +39079,7 @@
         <v>339</v>
       </c>
       <c r="I307" s="6"/>
-      <c r="J307" s="71"/>
+      <c r="J307" s="70"/>
       <c r="K307" s="19">
         <v>20</v>
       </c>
@@ -39209,7 +39204,7 @@
         <v>339</v>
       </c>
       <c r="I308" s="6"/>
-      <c r="J308" s="71"/>
+      <c r="J308" s="70"/>
       <c r="K308" s="19">
         <v>20</v>
       </c>
@@ -39326,7 +39321,7 @@
         <v>342</v>
       </c>
       <c r="I309" s="6"/>
-      <c r="J309" s="71"/>
+      <c r="J309" s="70"/>
       <c r="K309" s="21"/>
       <c r="L309" s="21"/>
       <c r="M309" s="21"/>
@@ -39445,7 +39440,7 @@
         <v>341</v>
       </c>
       <c r="I310" s="6"/>
-      <c r="J310" s="71"/>
+      <c r="J310" s="70"/>
       <c r="K310" s="19">
         <v>0</v>
       </c>
@@ -39570,7 +39565,7 @@
         <v>341</v>
       </c>
       <c r="I311" s="6"/>
-      <c r="J311" s="71"/>
+      <c r="J311" s="70"/>
       <c r="K311" s="19">
         <v>20</v>
       </c>
@@ -39687,7 +39682,7 @@
         <v>341</v>
       </c>
       <c r="I312" s="6"/>
-      <c r="J312" s="71"/>
+      <c r="J312" s="70"/>
       <c r="K312" s="21"/>
       <c r="L312" s="21"/>
       <c r="M312" s="21"/>
@@ -39804,7 +39799,7 @@
         <v>341</v>
       </c>
       <c r="I313" s="6"/>
-      <c r="J313" s="71"/>
+      <c r="J313" s="70"/>
       <c r="K313" s="21"/>
       <c r="L313" s="21"/>
       <c r="M313" s="21"/>
@@ -39923,7 +39918,7 @@
         <v>341</v>
       </c>
       <c r="I314" s="6"/>
-      <c r="J314" s="71"/>
+      <c r="J314" s="70"/>
       <c r="K314" s="19">
         <v>20</v>
       </c>
@@ -40048,7 +40043,7 @@
         <v>341</v>
       </c>
       <c r="I315" s="6"/>
-      <c r="J315" s="71"/>
+      <c r="J315" s="70"/>
       <c r="K315" s="21"/>
       <c r="L315" s="21"/>
       <c r="M315" s="21"/>
@@ -40167,7 +40162,7 @@
         <v>341</v>
       </c>
       <c r="I316" s="6"/>
-      <c r="J316" s="71"/>
+      <c r="J316" s="70"/>
       <c r="K316" s="21"/>
       <c r="L316" s="21"/>
       <c r="M316" s="21"/>
@@ -40282,7 +40277,7 @@
         <v>341</v>
       </c>
       <c r="I317" s="6"/>
-      <c r="J317" s="71"/>
+      <c r="J317" s="70"/>
       <c r="K317" s="21"/>
       <c r="L317" s="21"/>
       <c r="M317" s="21"/>
@@ -40397,7 +40392,7 @@
         <v>341</v>
       </c>
       <c r="I318" s="6"/>
-      <c r="J318" s="71"/>
+      <c r="J318" s="70"/>
       <c r="K318" s="21"/>
       <c r="L318" s="21"/>
       <c r="M318" s="21"/>
@@ -40516,7 +40511,7 @@
         <v>341</v>
       </c>
       <c r="I319" s="6"/>
-      <c r="J319" s="71"/>
+      <c r="J319" s="70"/>
       <c r="K319" s="19">
         <v>20</v>
       </c>
@@ -40641,7 +40636,7 @@
         <v>341</v>
       </c>
       <c r="I320" s="6"/>
-      <c r="J320" s="71"/>
+      <c r="J320" s="70"/>
       <c r="K320" s="19">
         <v>40</v>
       </c>
@@ -40766,7 +40761,7 @@
         <v>340</v>
       </c>
       <c r="I321" s="6"/>
-      <c r="J321" s="71"/>
+      <c r="J321" s="70"/>
       <c r="K321" s="19">
         <v>20</v>
       </c>
@@ -40891,7 +40886,7 @@
         <v>340</v>
       </c>
       <c r="I322" s="6"/>
-      <c r="J322" s="71"/>
+      <c r="J322" s="70"/>
       <c r="K322" s="19">
         <v>20</v>
       </c>
@@ -41010,7 +41005,7 @@
         <v>340</v>
       </c>
       <c r="I323" s="6"/>
-      <c r="J323" s="71"/>
+      <c r="J323" s="70"/>
       <c r="K323" s="19">
         <v>20</v>
       </c>
@@ -41129,7 +41124,7 @@
         <v>340</v>
       </c>
       <c r="I324" s="6"/>
-      <c r="J324" s="71"/>
+      <c r="J324" s="70"/>
       <c r="K324" s="19">
         <v>10</v>
       </c>
@@ -41248,7 +41243,7 @@
         <v>340</v>
       </c>
       <c r="I325" s="6"/>
-      <c r="J325" s="71"/>
+      <c r="J325" s="70"/>
       <c r="K325" s="21"/>
       <c r="L325" s="21"/>
       <c r="M325" s="19">
@@ -41365,7 +41360,7 @@
         <v>339</v>
       </c>
       <c r="I326" s="6"/>
-      <c r="J326" s="71"/>
+      <c r="J326" s="70"/>
       <c r="K326" s="19">
         <v>40</v>
       </c>
@@ -41490,7 +41485,7 @@
         <v>339</v>
       </c>
       <c r="I327" s="6"/>
-      <c r="J327" s="71"/>
+      <c r="J327" s="70"/>
       <c r="K327" s="19">
         <v>20</v>
       </c>
@@ -41615,7 +41610,7 @@
         <v>339</v>
       </c>
       <c r="I328" s="6"/>
-      <c r="J328" s="71"/>
+      <c r="J328" s="70"/>
       <c r="K328" s="21"/>
       <c r="L328" s="21"/>
       <c r="M328" s="21"/>
@@ -41734,7 +41729,7 @@
         <v>339</v>
       </c>
       <c r="I329" s="6"/>
-      <c r="J329" s="71"/>
+      <c r="J329" s="70"/>
       <c r="K329" s="21"/>
       <c r="L329" s="21"/>
       <c r="M329" s="21"/>
@@ -41851,7 +41846,7 @@
         <v>339</v>
       </c>
       <c r="I330" s="6"/>
-      <c r="J330" s="71"/>
+      <c r="J330" s="70"/>
       <c r="K330" s="21"/>
       <c r="L330" s="21"/>
       <c r="M330" s="21"/>
@@ -41970,7 +41965,7 @@
         <v>339</v>
       </c>
       <c r="I331" s="6"/>
-      <c r="J331" s="71"/>
+      <c r="J331" s="70"/>
       <c r="K331" s="19">
         <v>0</v>
       </c>
@@ -42087,7 +42082,7 @@
         <v>339</v>
       </c>
       <c r="I332" s="6"/>
-      <c r="J332" s="71"/>
+      <c r="J332" s="70"/>
       <c r="K332" s="19">
         <v>20</v>
       </c>
@@ -42206,7 +42201,7 @@
         <v>339</v>
       </c>
       <c r="I333" s="6"/>
-      <c r="J333" s="71"/>
+      <c r="J333" s="70"/>
       <c r="K333" s="19">
         <v>20</v>
       </c>
@@ -42325,7 +42320,7 @@
         <v>342</v>
       </c>
       <c r="I334" s="6"/>
-      <c r="J334" s="71"/>
+      <c r="J334" s="70"/>
       <c r="K334" s="21"/>
       <c r="L334" s="21"/>
       <c r="M334" s="21"/>
@@ -42440,7 +42435,7 @@
         <v>339</v>
       </c>
       <c r="I335" s="6"/>
-      <c r="J335" s="71"/>
+      <c r="J335" s="70"/>
       <c r="K335" s="19">
         <v>20</v>
       </c>
@@ -42563,7 +42558,7 @@
         <v>339</v>
       </c>
       <c r="I336" s="6"/>
-      <c r="J336" s="71"/>
+      <c r="J336" s="70"/>
       <c r="K336" s="19">
         <v>10</v>
       </c>
@@ -42682,7 +42677,7 @@
         <v>339</v>
       </c>
       <c r="I337" s="6"/>
-      <c r="J337" s="71"/>
+      <c r="J337" s="70"/>
       <c r="K337" s="21"/>
       <c r="L337" s="21"/>
       <c r="M337" s="21"/>
@@ -42799,7 +42794,7 @@
         <v>339</v>
       </c>
       <c r="I338" s="6"/>
-      <c r="J338" s="71"/>
+      <c r="J338" s="70"/>
       <c r="K338" s="21"/>
       <c r="L338" s="21"/>
       <c r="M338" s="21"/>
@@ -42916,7 +42911,7 @@
         <v>339</v>
       </c>
       <c r="I339" s="6"/>
-      <c r="J339" s="71"/>
+      <c r="J339" s="70"/>
       <c r="K339" s="19">
         <v>0</v>
       </c>
@@ -43039,7 +43034,7 @@
         <v>341</v>
       </c>
       <c r="I340" s="6"/>
-      <c r="J340" s="71"/>
+      <c r="J340" s="70"/>
       <c r="K340" s="19">
         <v>20</v>
       </c>
@@ -43154,7 +43149,7 @@
         <v>341</v>
       </c>
       <c r="I341" s="6"/>
-      <c r="J341" s="71"/>
+      <c r="J341" s="70"/>
       <c r="K341" s="21"/>
       <c r="L341" s="21"/>
       <c r="M341" s="21"/>
@@ -43269,7 +43264,7 @@
         <v>341</v>
       </c>
       <c r="I342" s="6"/>
-      <c r="J342" s="71"/>
+      <c r="J342" s="70"/>
       <c r="K342" s="21"/>
       <c r="L342" s="21"/>
       <c r="M342" s="21"/>
@@ -43388,7 +43383,7 @@
         <v>341</v>
       </c>
       <c r="I343" s="6"/>
-      <c r="J343" s="71"/>
+      <c r="J343" s="70"/>
       <c r="K343" s="21"/>
       <c r="L343" s="19">
         <v>20</v>
@@ -43505,7 +43500,7 @@
         <v>341</v>
       </c>
       <c r="I344" s="6"/>
-      <c r="J344" s="71"/>
+      <c r="J344" s="70"/>
       <c r="K344" s="19">
         <v>40</v>
       </c>
@@ -43628,7 +43623,7 @@
         <v>341</v>
       </c>
       <c r="I345" s="6"/>
-      <c r="J345" s="71"/>
+      <c r="J345" s="70"/>
       <c r="K345" s="21"/>
       <c r="L345" s="21"/>
       <c r="M345" s="21"/>
@@ -43743,7 +43738,7 @@
         <v>341</v>
       </c>
       <c r="I346" s="6"/>
-      <c r="J346" s="71"/>
+      <c r="J346" s="70"/>
       <c r="K346" s="21"/>
       <c r="L346" s="19">
         <v>0</v>
@@ -43860,7 +43855,7 @@
         <v>341</v>
       </c>
       <c r="I347" s="6"/>
-      <c r="J347" s="71"/>
+      <c r="J347" s="70"/>
       <c r="K347" s="19">
         <v>0</v>
       </c>
@@ -43983,7 +43978,7 @@
         <v>341</v>
       </c>
       <c r="I348" s="6"/>
-      <c r="J348" s="71"/>
+      <c r="J348" s="70"/>
       <c r="K348" s="21"/>
       <c r="L348" s="19">
         <v>20</v>
@@ -44098,7 +44093,7 @@
         <v>341</v>
       </c>
       <c r="I349" s="6"/>
-      <c r="J349" s="71"/>
+      <c r="J349" s="70"/>
       <c r="K349" s="19">
         <v>40</v>
       </c>
@@ -44221,7 +44216,7 @@
         <v>340</v>
       </c>
       <c r="I350" s="6"/>
-      <c r="J350" s="71"/>
+      <c r="J350" s="70"/>
       <c r="K350" s="21"/>
       <c r="L350" s="21"/>
       <c r="M350" s="21"/>
@@ -44338,7 +44333,7 @@
         <v>340</v>
       </c>
       <c r="I351" s="6"/>
-      <c r="J351" s="71"/>
+      <c r="J351" s="70"/>
       <c r="K351" s="21"/>
       <c r="L351" s="21"/>
       <c r="M351" s="21"/>
@@ -44453,7 +44448,7 @@
         <v>340</v>
       </c>
       <c r="I352" s="6"/>
-      <c r="J352" s="71"/>
+      <c r="J352" s="70"/>
       <c r="K352" s="21"/>
       <c r="L352" s="21"/>
       <c r="M352" s="21"/>
@@ -44568,7 +44563,7 @@
         <v>340</v>
       </c>
       <c r="I353" s="6"/>
-      <c r="J353" s="71"/>
+      <c r="J353" s="70"/>
       <c r="K353" s="19">
         <v>20</v>
       </c>
@@ -44689,7 +44684,7 @@
         <v>340</v>
       </c>
       <c r="I354" s="6"/>
-      <c r="J354" s="71"/>
+      <c r="J354" s="70"/>
       <c r="K354" s="19">
         <v>20</v>
       </c>
@@ -44806,7 +44801,7 @@
         <v>340</v>
       </c>
       <c r="I355" s="6"/>
-      <c r="J355" s="71"/>
+      <c r="J355" s="70"/>
       <c r="K355" s="21"/>
       <c r="L355" s="21"/>
       <c r="M355" s="21"/>
@@ -44921,7 +44916,7 @@
         <v>340</v>
       </c>
       <c r="I356" s="6"/>
-      <c r="J356" s="71"/>
+      <c r="J356" s="70"/>
       <c r="K356" s="19">
         <v>20</v>
       </c>
@@ -45038,7 +45033,7 @@
         <v>340</v>
       </c>
       <c r="I357" s="6"/>
-      <c r="J357" s="71"/>
+      <c r="J357" s="70"/>
       <c r="K357" s="21"/>
       <c r="L357" s="21"/>
       <c r="M357" s="21"/>
@@ -45155,7 +45150,7 @@
         <v>341</v>
       </c>
       <c r="I358" s="6"/>
-      <c r="J358" s="71"/>
+      <c r="J358" s="70"/>
       <c r="K358" s="19">
         <v>10</v>
       </c>
@@ -45276,7 +45271,7 @@
         <v>340</v>
       </c>
       <c r="I359" s="6"/>
-      <c r="J359" s="71"/>
+      <c r="J359" s="70"/>
       <c r="K359" s="19">
         <v>10</v>
       </c>
@@ -45393,7 +45388,7 @@
         <v>340</v>
       </c>
       <c r="I360" s="6"/>
-      <c r="J360" s="71"/>
+      <c r="J360" s="70"/>
       <c r="K360" s="19">
         <v>20</v>
       </c>
@@ -45510,7 +45505,7 @@
         <v>340</v>
       </c>
       <c r="I361" s="6"/>
-      <c r="J361" s="71"/>
+      <c r="J361" s="70"/>
       <c r="K361" s="19">
         <v>120</v>
       </c>
@@ -45629,7 +45624,7 @@
         <v>340</v>
       </c>
       <c r="I362" s="6"/>
-      <c r="J362" s="71"/>
+      <c r="J362" s="70"/>
       <c r="K362" s="21"/>
       <c r="L362" s="21"/>
       <c r="M362" s="21"/>
@@ -45744,7 +45739,7 @@
         <v>342</v>
       </c>
       <c r="I363" s="6"/>
-      <c r="J363" s="71"/>
+      <c r="J363" s="70"/>
       <c r="K363" s="19">
         <v>126</v>
       </c>
@@ -45869,7 +45864,7 @@
         <v>342</v>
       </c>
       <c r="I364" s="6"/>
-      <c r="J364" s="71"/>
+      <c r="J364" s="70"/>
       <c r="K364" s="19">
         <v>252</v>
       </c>
@@ -45994,7 +45989,7 @@
         <v>342</v>
       </c>
       <c r="I365" s="6"/>
-      <c r="J365" s="71"/>
+      <c r="J365" s="70"/>
       <c r="K365" s="19">
         <v>200</v>
       </c>
@@ -46119,7 +46114,7 @@
         <v>342</v>
       </c>
       <c r="I366" s="6"/>
-      <c r="J366" s="71"/>
+      <c r="J366" s="70"/>
       <c r="K366" s="21"/>
       <c r="L366" s="21"/>
       <c r="M366" s="19">
@@ -46238,7 +46233,7 @@
         <v>341</v>
       </c>
       <c r="I367" s="6"/>
-      <c r="J367" s="71"/>
+      <c r="J367" s="70"/>
       <c r="K367" s="19">
         <v>80</v>
       </c>
@@ -46363,7 +46358,7 @@
         <v>341</v>
       </c>
       <c r="I368" s="6"/>
-      <c r="J368" s="71">
+      <c r="J368" s="70">
         <v>40</v>
       </c>
       <c r="K368" s="21"/>
@@ -46482,7 +46477,7 @@
         <v>341</v>
       </c>
       <c r="I369" s="6"/>
-      <c r="J369" s="71">
+      <c r="J369" s="70">
         <v>40</v>
       </c>
       <c r="K369" s="21"/>
@@ -46603,7 +46598,7 @@
         <v>341</v>
       </c>
       <c r="I370" s="6"/>
-      <c r="J370" s="71"/>
+      <c r="J370" s="70"/>
       <c r="K370" s="21"/>
       <c r="L370" s="21"/>
       <c r="M370" s="21"/>
@@ -46720,7 +46715,7 @@
         <v>341</v>
       </c>
       <c r="I371" s="6"/>
-      <c r="J371" s="71">
+      <c r="J371" s="70">
         <v>10</v>
       </c>
       <c r="K371" s="21"/>
@@ -46843,7 +46838,7 @@
         <v>341</v>
       </c>
       <c r="I372" s="6"/>
-      <c r="J372" s="71">
+      <c r="J372" s="70">
         <v>10</v>
       </c>
       <c r="K372" s="21"/>
@@ -46962,7 +46957,7 @@
         <v>341</v>
       </c>
       <c r="I373" s="6"/>
-      <c r="J373" s="71">
+      <c r="J373" s="70">
         <v>10</v>
       </c>
       <c r="K373" s="21"/>
@@ -47087,7 +47082,7 @@
         <v>341</v>
       </c>
       <c r="I374" s="6"/>
-      <c r="J374" s="71"/>
+      <c r="J374" s="70"/>
       <c r="K374" s="21"/>
       <c r="L374" s="21"/>
       <c r="M374" s="21"/>
@@ -47204,7 +47199,7 @@
         <v>341</v>
       </c>
       <c r="I375" s="6"/>
-      <c r="J375" s="71"/>
+      <c r="J375" s="70"/>
       <c r="K375" s="21"/>
       <c r="L375" s="21"/>
       <c r="M375" s="21"/>
@@ -47321,7 +47316,7 @@
         <v>341</v>
       </c>
       <c r="I376" s="6"/>
-      <c r="J376" s="71"/>
+      <c r="J376" s="70"/>
       <c r="K376" s="19">
         <v>20</v>
       </c>
@@ -47446,7 +47441,7 @@
         <v>341</v>
       </c>
       <c r="I377" s="6"/>
-      <c r="J377" s="71"/>
+      <c r="J377" s="70"/>
       <c r="K377" s="21"/>
       <c r="L377" s="21"/>
       <c r="M377" s="21"/>
@@ -48906,7 +48901,7 @@
         <v>342</v>
       </c>
       <c r="I389" s="6"/>
-      <c r="J389" s="71"/>
+      <c r="J389" s="70"/>
       <c r="K389" s="19">
         <v>42</v>
       </c>
@@ -49031,7 +49026,7 @@
         <v>342</v>
       </c>
       <c r="I390" s="6"/>
-      <c r="J390" s="71"/>
+      <c r="J390" s="70"/>
       <c r="K390" s="19">
         <v>126</v>
       </c>
@@ -49156,7 +49151,7 @@
         <v>342</v>
       </c>
       <c r="I391" s="6"/>
-      <c r="J391" s="71"/>
+      <c r="J391" s="70"/>
       <c r="K391" s="21"/>
       <c r="L391" s="21"/>
       <c r="M391" s="21"/>
@@ -49271,7 +49266,7 @@
         <v>340</v>
       </c>
       <c r="I392" s="6"/>
-      <c r="J392" s="71">
+      <c r="J392" s="70">
         <v>10</v>
       </c>
       <c r="K392" s="19">
@@ -49394,7 +49389,7 @@
         <v>340</v>
       </c>
       <c r="I393" s="6"/>
-      <c r="J393" s="71">
+      <c r="J393" s="70">
         <v>40</v>
       </c>
       <c r="K393" s="21"/>
@@ -49515,7 +49510,7 @@
         <v>340</v>
       </c>
       <c r="I394" s="6"/>
-      <c r="J394" s="71">
+      <c r="J394" s="70">
         <v>40</v>
       </c>
       <c r="K394" s="21"/>
@@ -49636,7 +49631,7 @@
         <v>341</v>
       </c>
       <c r="I395" s="6"/>
-      <c r="J395" s="71">
+      <c r="J395" s="70">
         <v>40</v>
       </c>
       <c r="K395" s="21"/>
@@ -49755,7 +49750,7 @@
         <v>341</v>
       </c>
       <c r="I396" s="6"/>
-      <c r="J396" s="71">
+      <c r="J396" s="70">
         <v>20</v>
       </c>
       <c r="K396" s="21"/>
@@ -49876,7 +49871,7 @@
         <v>341</v>
       </c>
       <c r="I397" s="6"/>
-      <c r="J397" s="71">
+      <c r="J397" s="70">
         <v>40</v>
       </c>
       <c r="K397" s="21"/>
@@ -49995,7 +49990,7 @@
         <v>341</v>
       </c>
       <c r="I398" s="6"/>
-      <c r="J398" s="71">
+      <c r="J398" s="70">
         <v>10</v>
       </c>
       <c r="K398" s="21"/>
@@ -50116,7 +50111,7 @@
         <v>341</v>
       </c>
       <c r="I399" s="6"/>
-      <c r="J399" s="71"/>
+      <c r="J399" s="70"/>
       <c r="K399" s="21"/>
       <c r="L399" s="21"/>
       <c r="M399" s="21"/>
@@ -50231,7 +50226,7 @@
         <v>339</v>
       </c>
       <c r="I400" s="6"/>
-      <c r="J400" s="71">
+      <c r="J400" s="70">
         <v>10</v>
       </c>
       <c r="K400" s="21"/>
@@ -50352,7 +50347,7 @@
         <v>339</v>
       </c>
       <c r="I401" s="6"/>
-      <c r="J401" s="71">
+      <c r="J401" s="70">
         <v>80</v>
       </c>
       <c r="K401" s="21"/>
@@ -50473,7 +50468,7 @@
         <v>339</v>
       </c>
       <c r="I402" s="6"/>
-      <c r="J402" s="71"/>
+      <c r="J402" s="70"/>
       <c r="K402" s="19">
         <v>20</v>
       </c>
@@ -50590,7 +50585,7 @@
         <v>342</v>
       </c>
       <c r="I403" s="6"/>
-      <c r="J403" s="71">
+      <c r="J403" s="70">
         <v>32</v>
       </c>
       <c r="K403" s="21"/>
@@ -50709,7 +50704,7 @@
         <v>340</v>
       </c>
       <c r="I404" s="6"/>
-      <c r="J404" s="71">
+      <c r="J404" s="70">
         <v>80</v>
       </c>
       <c r="K404" s="21"/>
@@ -50832,7 +50827,7 @@
         <v>341</v>
       </c>
       <c r="I405" s="6"/>
-      <c r="J405" s="71"/>
+      <c r="J405" s="70"/>
       <c r="K405" s="21"/>
       <c r="L405" s="21"/>
       <c r="M405" s="19">
@@ -50953,7 +50948,7 @@
         <v>341</v>
       </c>
       <c r="I406" s="6"/>
-      <c r="J406" s="71">
+      <c r="J406" s="70">
         <v>40</v>
       </c>
       <c r="K406" s="19">
@@ -51080,7 +51075,7 @@
         <v>341</v>
       </c>
       <c r="I407" s="6"/>
-      <c r="J407" s="71"/>
+      <c r="J407" s="70"/>
       <c r="K407" s="21"/>
       <c r="L407" s="21"/>
       <c r="M407" s="21"/>
@@ -51197,7 +51192,7 @@
         <v>341</v>
       </c>
       <c r="I408" s="6"/>
-      <c r="J408" s="71"/>
+      <c r="J408" s="70"/>
       <c r="K408" s="19">
         <v>40</v>
       </c>
@@ -51314,7 +51309,7 @@
         <v>341</v>
       </c>
       <c r="I409" s="6"/>
-      <c r="J409" s="71">
+      <c r="J409" s="70">
         <v>20</v>
       </c>
       <c r="K409" s="21"/>
@@ -51431,7 +51426,7 @@
         <v>341</v>
       </c>
       <c r="I410" s="6"/>
-      <c r="J410" s="71">
+      <c r="J410" s="70">
         <v>40</v>
       </c>
       <c r="K410" s="21"/>
@@ -51552,7 +51547,7 @@
         <v>341</v>
       </c>
       <c r="I411" s="6"/>
-      <c r="J411" s="71">
+      <c r="J411" s="70">
         <v>20</v>
       </c>
       <c r="K411" s="19">
@@ -51679,7 +51674,7 @@
         <v>341</v>
       </c>
       <c r="I412" s="6"/>
-      <c r="J412" s="71">
+      <c r="J412" s="70">
         <v>40</v>
       </c>
       <c r="K412" s="19">
@@ -51806,7 +51801,7 @@
         <v>341</v>
       </c>
       <c r="I413" s="6"/>
-      <c r="J413" s="71">
+      <c r="J413" s="70">
         <v>40</v>
       </c>
       <c r="K413" s="19">
@@ -51933,7 +51928,7 @@
         <v>339</v>
       </c>
       <c r="I414" s="6"/>
-      <c r="J414" s="71"/>
+      <c r="J414" s="70"/>
       <c r="K414" s="21"/>
       <c r="L414" s="21"/>
       <c r="M414" s="21"/>
@@ -52052,7 +52047,7 @@
         <v>341</v>
       </c>
       <c r="I415" s="6"/>
-      <c r="J415" s="71"/>
+      <c r="J415" s="70"/>
       <c r="K415" s="21"/>
       <c r="L415" s="21"/>
       <c r="M415" s="21"/>
@@ -52167,7 +52162,7 @@
         <v>341</v>
       </c>
       <c r="I416" s="6"/>
-      <c r="J416" s="71">
+      <c r="J416" s="70">
         <v>80</v>
       </c>
       <c r="K416" s="21"/>
@@ -52284,7 +52279,7 @@
         <v>342</v>
       </c>
       <c r="I417" s="6"/>
-      <c r="J417" s="71"/>
+      <c r="J417" s="70"/>
       <c r="K417" s="19">
         <v>200</v>
       </c>
@@ -52486,84 +52481,31 @@
       <c r="AO418" s="13"/>
     </row>
     <row r="419" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="A419" s="70"/>
-      <c r="B419" s="70"/>
-      <c r="C419" s="70"/>
-      <c r="D419" s="70"/>
-      <c r="E419" s="70"/>
-      <c r="F419" s="70"/>
-      <c r="G419" s="70"/>
-      <c r="H419" s="70"/>
-      <c r="I419" s="70"/>
-      <c r="J419" s="71"/>
-      <c r="K419" s="71"/>
-      <c r="L419" s="71"/>
-      <c r="M419" s="71"/>
-      <c r="N419" s="71"/>
-      <c r="O419" s="71"/>
-      <c r="P419" s="71"/>
-      <c r="Q419" s="71"/>
-      <c r="R419" s="71"/>
-      <c r="S419" s="70"/>
-      <c r="T419" s="70"/>
-      <c r="U419" s="70"/>
-      <c r="V419" s="70"/>
-      <c r="W419" s="70"/>
-      <c r="X419" s="70"/>
-      <c r="Y419" s="70"/>
-      <c r="Z419" s="70"/>
-      <c r="AA419" s="70"/>
-      <c r="AB419" s="70"/>
-      <c r="AC419" s="70"/>
-      <c r="AD419" s="70"/>
-      <c r="AE419" s="70"/>
-      <c r="AF419" s="72"/>
-      <c r="AG419" s="70"/>
-      <c r="AH419" s="70"/>
-      <c r="AJ419" s="70"/>
-      <c r="AK419" s="70"/>
-      <c r="AO419" s="73"/>
+      <c r="J419" s="70"/>
+      <c r="K419" s="70"/>
+      <c r="L419" s="70"/>
+      <c r="M419" s="70"/>
+      <c r="N419" s="70"/>
+      <c r="O419" s="70"/>
+      <c r="P419" s="70"/>
+      <c r="Q419" s="70"/>
+      <c r="R419" s="70"/>
+      <c r="AO419" s="16"/>
     </row>
     <row r="420" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="A420" s="70"/>
-      <c r="B420" s="70"/>
-      <c r="C420" s="70"/>
-      <c r="D420" s="70"/>
-      <c r="E420" s="70"/>
-      <c r="F420" s="70"/>
-      <c r="G420" s="70"/>
-      <c r="H420" s="70"/>
-      <c r="I420" s="70"/>
-      <c r="J420" s="71"/>
-      <c r="K420" s="71"/>
-      <c r="L420" s="71"/>
-      <c r="M420" s="71"/>
-      <c r="N420" s="71"/>
-      <c r="O420" s="71"/>
-      <c r="P420" s="71"/>
-      <c r="Q420" s="71"/>
-      <c r="R420" s="71"/>
-      <c r="S420" s="70"/>
-      <c r="T420" s="70"/>
-      <c r="U420" s="70"/>
-      <c r="V420" s="70"/>
-      <c r="W420" s="70"/>
-      <c r="X420" s="70"/>
-      <c r="Y420" s="70"/>
-      <c r="Z420" s="70"/>
-      <c r="AA420" s="70"/>
-      <c r="AB420" s="70"/>
-      <c r="AC420" s="70" t="s">
+      <c r="J420" s="70"/>
+      <c r="K420" s="70"/>
+      <c r="L420" s="70"/>
+      <c r="M420" s="70"/>
+      <c r="N420" s="70"/>
+      <c r="O420" s="70"/>
+      <c r="P420" s="70"/>
+      <c r="Q420" s="70"/>
+      <c r="R420" s="70"/>
+      <c r="AC420" t="s">
         <v>357</v>
       </c>
-      <c r="AD420" s="70"/>
-      <c r="AE420" s="70"/>
-      <c r="AF420" s="72"/>
-      <c r="AG420" s="70"/>
-      <c r="AH420" s="70"/>
-      <c r="AJ420" s="70"/>
-      <c r="AK420" s="70"/>
-      <c r="AO420" s="73"/>
+      <c r="AO420" s="16"/>
     </row>
     <row r="421" spans="1:41" ht="29" x14ac:dyDescent="0.35">
       <c r="J421" s="69" t="s">
@@ -52596,42 +52538,42 @@
       <c r="AF421"/>
     </row>
     <row r="422" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="I422" s="77" t="s">
+      <c r="I422" s="74" t="s">
         <v>357</v>
       </c>
-      <c r="J422" s="82">
+      <c r="J422" s="79">
         <f t="shared" ref="J422:AF422" si="125">+J418/40</f>
         <v>26.6</v>
       </c>
-      <c r="K422" s="83">
+      <c r="K422" s="80">
         <f t="shared" si="125"/>
         <v>153.27500000000001</v>
       </c>
-      <c r="L422" s="83">
+      <c r="L422" s="80">
         <f t="shared" si="125"/>
         <v>100.15</v>
       </c>
-      <c r="M422" s="83">
+      <c r="M422" s="80">
         <f t="shared" si="125"/>
         <v>108.15</v>
       </c>
-      <c r="N422" s="82">
+      <c r="N422" s="79">
         <f t="shared" si="125"/>
         <v>361.57499999999999</v>
       </c>
-      <c r="O422" s="83">
+      <c r="O422" s="80">
         <f t="shared" si="125"/>
         <v>261.02499999999998</v>
       </c>
-      <c r="P422" s="83">
+      <c r="P422" s="80">
         <f t="shared" si="125"/>
         <v>184.72499999999999</v>
       </c>
-      <c r="Q422" s="83">
+      <c r="Q422" s="80">
         <f t="shared" si="125"/>
         <v>178.625</v>
       </c>
-      <c r="R422" s="82">
+      <c r="R422" s="79">
         <f t="shared" si="125"/>
         <v>624.375</v>
       </c>
@@ -52709,13 +52651,14 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AH1:AH2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -52728,14 +52671,13 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AN1:AN2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AH1:AH2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52765,22 +52707,22 @@
   <sheetData>
     <row r="3" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="4:8" ht="22.5" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="D4" s="95" t="s">
+      <c r="D4" s="92" t="s">
         <v>343</v>
       </c>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="97"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="94"/>
     </row>
     <row r="5" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D5" s="23" t="s">
         <v>373</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
     </row>
     <row r="6" spans="4:8" x14ac:dyDescent="0.35">
       <c r="D6" s="24" t="s">
@@ -52881,7 +52823,7 @@
       <c r="F11" s="29">
         <v>500</v>
       </c>
-      <c r="G11" s="78">
+      <c r="G11" s="75">
         <f>'STT Report'!J418/40</f>
         <v>26.6</v>
       </c>
@@ -53056,7 +52998,7 @@
       <c r="L22" s="42"/>
       <c r="M22" s="42"/>
     </row>
-    <row r="23" spans="3:13" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:13" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C23" s="43" t="s">
         <v>359</v>
       </c>
@@ -53122,7 +53064,7 @@
       <c r="K24" s="51">
         <v>4.05</v>
       </c>
-      <c r="L24" s="79">
+      <c r="L24" s="76">
         <f>I24+J24+G24+H24+K24</f>
         <v>340.70499999999998</v>
       </c>
@@ -53162,7 +53104,7 @@
       <c r="K25" s="57">
         <v>13.5</v>
       </c>
-      <c r="L25" s="81">
+      <c r="L25" s="78">
         <f>I25+J25+G25+H25+K25</f>
         <v>416.96899999999999</v>
       </c>
@@ -53202,7 +53144,7 @@
       <c r="K26" s="57">
         <v>2.25</v>
       </c>
-      <c r="L26" s="81">
+      <c r="L26" s="78">
         <f>I26+J26+G26+H26+K26</f>
         <v>153.5</v>
       </c>
@@ -53242,7 +53184,7 @@
       <c r="K27" s="63">
         <v>6.8</v>
       </c>
-      <c r="L27" s="80">
+      <c r="L27" s="77">
         <f>I27+J27+G27+H27+K27</f>
         <v>199.96</v>
       </c>
@@ -53252,10 +53194,10 @@
       </c>
     </row>
     <row r="28" spans="3:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C28" s="99" t="s">
+      <c r="C28" s="96" t="s">
         <v>372</v>
       </c>
-      <c r="D28" s="100"/>
+      <c r="D28" s="97"/>
       <c r="E28" s="65">
         <f t="shared" ref="E28:L28" si="4">SUM(E24:E27)</f>
         <v>2500</v>
